--- a/outputs/roster-import/zla-seniority-roster-template.xlsx
+++ b/outputs/roster-import/zla-seniority-roster-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster" sheetId="1" r:id="Rb101f455933a4d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster" sheetId="1" r:id="R80a49ae9499a4922"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -46,7 +46,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -68,8 +68,18 @@
         <x:fgColor rgb="FFFFFCED"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF244C38"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFCED"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="13">
+  <x:borders count="14">
     <x:border/>
     <x:border>
       <x:right style="thin">
@@ -179,11 +189,19 @@
         <x:color rgb="FFDCE5DF"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFDCE5DF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFDCE5DF"/>
+      </x:right>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="79">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -305,6 +323,34 @@
     <x:xf numFmtId="201" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -313,8 +359,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RosterImportTable" displayName="RosterImportTable" ref="A5:K8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="11">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RosterImportTable" displayName="RosterImportTable" ref="A5:L8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:L8"/>
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="profile_id"/>
     <x:tableColumn id="2" name="area_code"/>
     <x:tableColumn id="3" name="seniority_rank"/>
@@ -326,6 +373,7 @@
     <x:tableColumn id="9" name="bid_role"/>
     <x:tableColumn id="10" name="seniority_date"/>
     <x:tableColumn id="11" name="active"/>
+    <x:tableColumn id="12" name="leave_allowance_hours"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -537,6 +585,7 @@
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="23" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" ht="24" customHeight="1">
@@ -556,7 +605,7 @@
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="3" t="str">
-        <x:v>One row per BUE. Keep profile_id blank for new people. Blank email and phone cells preserve existing values.</x:v>
+        <x:v>One row per BUE. Enter leave allowance in hours. Keep profile_id blank for new people. Blank email and phone cells preserve existing values.</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -613,8 +662,11 @@
       <x:c r="J5" s="16" t="str">
         <x:v>seniority_date</x:v>
       </x:c>
-      <x:c r="K5" s="17" t="str">
+      <x:c r="K5" s="16" t="str">
         <x:v>active</x:v>
+      </x:c>
+      <x:c r="L5" s="72" t="str">
+        <x:v>leave_allowance_hours</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -644,8 +696,11 @@
       <x:c r="J6" s="49" t="n">
         <x:v>38484</x:v>
       </x:c>
-      <x:c r="K6" s="50" t="str">
+      <x:c r="K6" s="47" t="str">
         <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="L6" s="78" t="n">
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -673,8 +728,11 @@
       <x:c r="J7" s="54" t="n">
         <x:v>39711</x:v>
       </x:c>
-      <x:c r="K7" s="55" t="str">
+      <x:c r="K7" s="52" t="str">
         <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="L7" s="78" t="n">
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -702,8 +760,11 @@
       <x:c r="J8" s="59" t="n">
         <x:v>40212</x:v>
       </x:c>
-      <x:c r="K8" s="60" t="str">
+      <x:c r="K8" s="57" t="str">
         <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="L8" s="78" t="n">
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -717,7 +778,8 @@
       <x:c r="H9" s="62"/>
       <x:c r="I9" s="62"/>
       <x:c r="J9" s="64"/>
-      <x:c r="K9" s="62"/>
+      <x:c r="K9" s="65"/>
+      <x:c r="L9" s="78"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="61"/>
@@ -730,7 +792,8 @@
       <x:c r="H10" s="62"/>
       <x:c r="I10" s="62"/>
       <x:c r="J10" s="64"/>
-      <x:c r="K10" s="62"/>
+      <x:c r="K10" s="65"/>
+      <x:c r="L10" s="78"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="61"/>
@@ -743,7 +806,8 @@
       <x:c r="H11" s="62"/>
       <x:c r="I11" s="62"/>
       <x:c r="J11" s="64"/>
-      <x:c r="K11" s="62"/>
+      <x:c r="K11" s="65"/>
+      <x:c r="L11" s="78"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="61"/>
@@ -756,7 +820,8 @@
       <x:c r="H12" s="62"/>
       <x:c r="I12" s="62"/>
       <x:c r="J12" s="64"/>
-      <x:c r="K12" s="62"/>
+      <x:c r="K12" s="65"/>
+      <x:c r="L12" s="78"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="61"/>
@@ -769,7 +834,8 @@
       <x:c r="H13" s="62"/>
       <x:c r="I13" s="62"/>
       <x:c r="J13" s="64"/>
-      <x:c r="K13" s="62"/>
+      <x:c r="K13" s="65"/>
+      <x:c r="L13" s="78"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="61"/>
@@ -782,7 +848,8 @@
       <x:c r="H14" s="62"/>
       <x:c r="I14" s="62"/>
       <x:c r="J14" s="64"/>
-      <x:c r="K14" s="62"/>
+      <x:c r="K14" s="65"/>
+      <x:c r="L14" s="78"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="61"/>
@@ -795,7 +862,8 @@
       <x:c r="H15" s="62"/>
       <x:c r="I15" s="62"/>
       <x:c r="J15" s="64"/>
-      <x:c r="K15" s="62"/>
+      <x:c r="K15" s="65"/>
+      <x:c r="L15" s="78"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="61"/>
@@ -808,7 +876,8 @@
       <x:c r="H16" s="62"/>
       <x:c r="I16" s="62"/>
       <x:c r="J16" s="64"/>
-      <x:c r="K16" s="62"/>
+      <x:c r="K16" s="65"/>
+      <x:c r="L16" s="78"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="61"/>
@@ -821,7 +890,8 @@
       <x:c r="H17" s="62"/>
       <x:c r="I17" s="62"/>
       <x:c r="J17" s="64"/>
-      <x:c r="K17" s="62"/>
+      <x:c r="K17" s="65"/>
+      <x:c r="L17" s="78"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="61"/>
@@ -834,7 +904,8 @@
       <x:c r="H18" s="62"/>
       <x:c r="I18" s="62"/>
       <x:c r="J18" s="64"/>
-      <x:c r="K18" s="62"/>
+      <x:c r="K18" s="65"/>
+      <x:c r="L18" s="78"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="61"/>
@@ -847,7 +918,8 @@
       <x:c r="H19" s="62"/>
       <x:c r="I19" s="62"/>
       <x:c r="J19" s="64"/>
-      <x:c r="K19" s="62"/>
+      <x:c r="K19" s="65"/>
+      <x:c r="L19" s="78"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="61"/>
@@ -860,7 +932,8 @@
       <x:c r="H20" s="62"/>
       <x:c r="I20" s="62"/>
       <x:c r="J20" s="64"/>
-      <x:c r="K20" s="62"/>
+      <x:c r="K20" s="65"/>
+      <x:c r="L20" s="78"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="61"/>
@@ -873,7 +946,8 @@
       <x:c r="H21" s="62"/>
       <x:c r="I21" s="62"/>
       <x:c r="J21" s="64"/>
-      <x:c r="K21" s="62"/>
+      <x:c r="K21" s="65"/>
+      <x:c r="L21" s="78"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="61"/>
@@ -886,7 +960,8 @@
       <x:c r="H22" s="62"/>
       <x:c r="I22" s="62"/>
       <x:c r="J22" s="64"/>
-      <x:c r="K22" s="62"/>
+      <x:c r="K22" s="65"/>
+      <x:c r="L22" s="78"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="61"/>
@@ -899,7 +974,8 @@
       <x:c r="H23" s="62"/>
       <x:c r="I23" s="62"/>
       <x:c r="J23" s="64"/>
-      <x:c r="K23" s="62"/>
+      <x:c r="K23" s="65"/>
+      <x:c r="L23" s="78"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="61"/>
@@ -912,7 +988,8 @@
       <x:c r="H24" s="62"/>
       <x:c r="I24" s="62"/>
       <x:c r="J24" s="64"/>
-      <x:c r="K24" s="62"/>
+      <x:c r="K24" s="65"/>
+      <x:c r="L24" s="78"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="61"/>
@@ -925,7 +1002,8 @@
       <x:c r="H25" s="62"/>
       <x:c r="I25" s="62"/>
       <x:c r="J25" s="64"/>
-      <x:c r="K25" s="62"/>
+      <x:c r="K25" s="65"/>
+      <x:c r="L25" s="78"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="61"/>
@@ -938,7 +1016,8 @@
       <x:c r="H26" s="62"/>
       <x:c r="I26" s="62"/>
       <x:c r="J26" s="64"/>
-      <x:c r="K26" s="62"/>
+      <x:c r="K26" s="65"/>
+      <x:c r="L26" s="78"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="61"/>
@@ -951,7 +1030,8 @@
       <x:c r="H27" s="62"/>
       <x:c r="I27" s="62"/>
       <x:c r="J27" s="64"/>
-      <x:c r="K27" s="62"/>
+      <x:c r="K27" s="65"/>
+      <x:c r="L27" s="78"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="61"/>
@@ -964,7 +1044,8 @@
       <x:c r="H28" s="62"/>
       <x:c r="I28" s="62"/>
       <x:c r="J28" s="64"/>
-      <x:c r="K28" s="62"/>
+      <x:c r="K28" s="65"/>
+      <x:c r="L28" s="78"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="61"/>
@@ -977,7 +1058,8 @@
       <x:c r="H29" s="62"/>
       <x:c r="I29" s="62"/>
       <x:c r="J29" s="64"/>
-      <x:c r="K29" s="62"/>
+      <x:c r="K29" s="65"/>
+      <x:c r="L29" s="78"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="61"/>
@@ -990,7 +1072,8 @@
       <x:c r="H30" s="62"/>
       <x:c r="I30" s="62"/>
       <x:c r="J30" s="64"/>
-      <x:c r="K30" s="62"/>
+      <x:c r="K30" s="65"/>
+      <x:c r="L30" s="78"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="61"/>
@@ -1003,7 +1086,8 @@
       <x:c r="H31" s="62"/>
       <x:c r="I31" s="62"/>
       <x:c r="J31" s="64"/>
-      <x:c r="K31" s="62"/>
+      <x:c r="K31" s="65"/>
+      <x:c r="L31" s="78"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="61"/>
@@ -1016,7 +1100,8 @@
       <x:c r="H32" s="62"/>
       <x:c r="I32" s="62"/>
       <x:c r="J32" s="64"/>
-      <x:c r="K32" s="62"/>
+      <x:c r="K32" s="65"/>
+      <x:c r="L32" s="78"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="61"/>
@@ -1029,7 +1114,8 @@
       <x:c r="H33" s="62"/>
       <x:c r="I33" s="62"/>
       <x:c r="J33" s="64"/>
-      <x:c r="K33" s="62"/>
+      <x:c r="K33" s="65"/>
+      <x:c r="L33" s="78"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="61"/>
@@ -1042,7 +1128,8 @@
       <x:c r="H34" s="62"/>
       <x:c r="I34" s="62"/>
       <x:c r="J34" s="64"/>
-      <x:c r="K34" s="62"/>
+      <x:c r="K34" s="65"/>
+      <x:c r="L34" s="78"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="61"/>
@@ -1055,7 +1142,8 @@
       <x:c r="H35" s="62"/>
       <x:c r="I35" s="62"/>
       <x:c r="J35" s="64"/>
-      <x:c r="K35" s="62"/>
+      <x:c r="K35" s="65"/>
+      <x:c r="L35" s="78"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="61"/>
@@ -1068,7 +1156,8 @@
       <x:c r="H36" s="62"/>
       <x:c r="I36" s="62"/>
       <x:c r="J36" s="64"/>
-      <x:c r="K36" s="62"/>
+      <x:c r="K36" s="65"/>
+      <x:c r="L36" s="78"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="61"/>
@@ -1081,7 +1170,8 @@
       <x:c r="H37" s="62"/>
       <x:c r="I37" s="62"/>
       <x:c r="J37" s="64"/>
-      <x:c r="K37" s="62"/>
+      <x:c r="K37" s="65"/>
+      <x:c r="L37" s="78"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="61"/>
@@ -1094,7 +1184,8 @@
       <x:c r="H38" s="62"/>
       <x:c r="I38" s="62"/>
       <x:c r="J38" s="64"/>
-      <x:c r="K38" s="62"/>
+      <x:c r="K38" s="65"/>
+      <x:c r="L38" s="78"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="61"/>
@@ -1107,7 +1198,8 @@
       <x:c r="H39" s="62"/>
       <x:c r="I39" s="62"/>
       <x:c r="J39" s="64"/>
-      <x:c r="K39" s="62"/>
+      <x:c r="K39" s="65"/>
+      <x:c r="L39" s="78"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="61"/>
@@ -1120,7 +1212,8 @@
       <x:c r="H40" s="62"/>
       <x:c r="I40" s="62"/>
       <x:c r="J40" s="64"/>
-      <x:c r="K40" s="62"/>
+      <x:c r="K40" s="65"/>
+      <x:c r="L40" s="78"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="61"/>
@@ -1133,7 +1226,8 @@
       <x:c r="H41" s="62"/>
       <x:c r="I41" s="62"/>
       <x:c r="J41" s="64"/>
-      <x:c r="K41" s="62"/>
+      <x:c r="K41" s="65"/>
+      <x:c r="L41" s="78"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="61"/>
@@ -1146,7 +1240,8 @@
       <x:c r="H42" s="62"/>
       <x:c r="I42" s="62"/>
       <x:c r="J42" s="64"/>
-      <x:c r="K42" s="62"/>
+      <x:c r="K42" s="65"/>
+      <x:c r="L42" s="78"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="61"/>
@@ -1159,7 +1254,8 @@
       <x:c r="H43" s="62"/>
       <x:c r="I43" s="62"/>
       <x:c r="J43" s="64"/>
-      <x:c r="K43" s="62"/>
+      <x:c r="K43" s="65"/>
+      <x:c r="L43" s="78"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="61"/>
@@ -1172,7 +1268,8 @@
       <x:c r="H44" s="62"/>
       <x:c r="I44" s="62"/>
       <x:c r="J44" s="64"/>
-      <x:c r="K44" s="62"/>
+      <x:c r="K44" s="65"/>
+      <x:c r="L44" s="78"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="61"/>
@@ -1185,7 +1282,8 @@
       <x:c r="H45" s="62"/>
       <x:c r="I45" s="62"/>
       <x:c r="J45" s="64"/>
-      <x:c r="K45" s="62"/>
+      <x:c r="K45" s="65"/>
+      <x:c r="L45" s="78"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="61"/>
@@ -1198,7 +1296,8 @@
       <x:c r="H46" s="62"/>
       <x:c r="I46" s="62"/>
       <x:c r="J46" s="64"/>
-      <x:c r="K46" s="62"/>
+      <x:c r="K46" s="65"/>
+      <x:c r="L46" s="78"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="61"/>
@@ -1211,7 +1310,8 @@
       <x:c r="H47" s="62"/>
       <x:c r="I47" s="62"/>
       <x:c r="J47" s="64"/>
-      <x:c r="K47" s="62"/>
+      <x:c r="K47" s="65"/>
+      <x:c r="L47" s="78"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="61"/>
@@ -1224,7 +1324,8 @@
       <x:c r="H48" s="62"/>
       <x:c r="I48" s="62"/>
       <x:c r="J48" s="64"/>
-      <x:c r="K48" s="62"/>
+      <x:c r="K48" s="65"/>
+      <x:c r="L48" s="78"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="61"/>
@@ -1237,7 +1338,8 @@
       <x:c r="H49" s="62"/>
       <x:c r="I49" s="62"/>
       <x:c r="J49" s="64"/>
-      <x:c r="K49" s="62"/>
+      <x:c r="K49" s="65"/>
+      <x:c r="L49" s="78"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="61"/>
@@ -1250,7 +1352,8 @@
       <x:c r="H50" s="62"/>
       <x:c r="I50" s="62"/>
       <x:c r="J50" s="64"/>
-      <x:c r="K50" s="62"/>
+      <x:c r="K50" s="65"/>
+      <x:c r="L50" s="78"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="61"/>
@@ -1263,7 +1366,8 @@
       <x:c r="H51" s="62"/>
       <x:c r="I51" s="62"/>
       <x:c r="J51" s="64"/>
-      <x:c r="K51" s="62"/>
+      <x:c r="K51" s="65"/>
+      <x:c r="L51" s="78"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="61"/>
@@ -1276,7 +1380,8 @@
       <x:c r="H52" s="62"/>
       <x:c r="I52" s="62"/>
       <x:c r="J52" s="64"/>
-      <x:c r="K52" s="62"/>
+      <x:c r="K52" s="65"/>
+      <x:c r="L52" s="78"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="61"/>
@@ -1289,7 +1394,8 @@
       <x:c r="H53" s="62"/>
       <x:c r="I53" s="62"/>
       <x:c r="J53" s="64"/>
-      <x:c r="K53" s="62"/>
+      <x:c r="K53" s="65"/>
+      <x:c r="L53" s="78"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="61"/>
@@ -1302,7 +1408,8 @@
       <x:c r="H54" s="62"/>
       <x:c r="I54" s="62"/>
       <x:c r="J54" s="64"/>
-      <x:c r="K54" s="62"/>
+      <x:c r="K54" s="65"/>
+      <x:c r="L54" s="78"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="61"/>
@@ -1315,7 +1422,8 @@
       <x:c r="H55" s="62"/>
       <x:c r="I55" s="62"/>
       <x:c r="J55" s="64"/>
-      <x:c r="K55" s="62"/>
+      <x:c r="K55" s="65"/>
+      <x:c r="L55" s="78"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="61"/>
@@ -1328,7 +1436,8 @@
       <x:c r="H56" s="62"/>
       <x:c r="I56" s="62"/>
       <x:c r="J56" s="64"/>
-      <x:c r="K56" s="62"/>
+      <x:c r="K56" s="65"/>
+      <x:c r="L56" s="78"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="61"/>
@@ -1341,7 +1450,8 @@
       <x:c r="H57" s="62"/>
       <x:c r="I57" s="62"/>
       <x:c r="J57" s="64"/>
-      <x:c r="K57" s="62"/>
+      <x:c r="K57" s="65"/>
+      <x:c r="L57" s="78"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="61"/>
@@ -1354,7 +1464,8 @@
       <x:c r="H58" s="62"/>
       <x:c r="I58" s="62"/>
       <x:c r="J58" s="64"/>
-      <x:c r="K58" s="62"/>
+      <x:c r="K58" s="65"/>
+      <x:c r="L58" s="78"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="61"/>
@@ -1367,7 +1478,8 @@
       <x:c r="H59" s="62"/>
       <x:c r="I59" s="62"/>
       <x:c r="J59" s="64"/>
-      <x:c r="K59" s="62"/>
+      <x:c r="K59" s="65"/>
+      <x:c r="L59" s="78"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="61"/>
@@ -1380,7 +1492,8 @@
       <x:c r="H60" s="62"/>
       <x:c r="I60" s="62"/>
       <x:c r="J60" s="64"/>
-      <x:c r="K60" s="62"/>
+      <x:c r="K60" s="65"/>
+      <x:c r="L60" s="78"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="61"/>
@@ -1393,7 +1506,8 @@
       <x:c r="H61" s="62"/>
       <x:c r="I61" s="62"/>
       <x:c r="J61" s="64"/>
-      <x:c r="K61" s="62"/>
+      <x:c r="K61" s="65"/>
+      <x:c r="L61" s="78"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="61"/>
@@ -1406,7 +1520,8 @@
       <x:c r="H62" s="62"/>
       <x:c r="I62" s="62"/>
       <x:c r="J62" s="64"/>
-      <x:c r="K62" s="62"/>
+      <x:c r="K62" s="65"/>
+      <x:c r="L62" s="78"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="61"/>
@@ -1419,7 +1534,8 @@
       <x:c r="H63" s="62"/>
       <x:c r="I63" s="62"/>
       <x:c r="J63" s="64"/>
-      <x:c r="K63" s="62"/>
+      <x:c r="K63" s="65"/>
+      <x:c r="L63" s="78"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="61"/>
@@ -1432,7 +1548,8 @@
       <x:c r="H64" s="62"/>
       <x:c r="I64" s="62"/>
       <x:c r="J64" s="64"/>
-      <x:c r="K64" s="62"/>
+      <x:c r="K64" s="65"/>
+      <x:c r="L64" s="78"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="61"/>
@@ -1445,7 +1562,8 @@
       <x:c r="H65" s="62"/>
       <x:c r="I65" s="62"/>
       <x:c r="J65" s="64"/>
-      <x:c r="K65" s="62"/>
+      <x:c r="K65" s="65"/>
+      <x:c r="L65" s="78"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="61"/>
@@ -1458,7 +1576,8 @@
       <x:c r="H66" s="62"/>
       <x:c r="I66" s="62"/>
       <x:c r="J66" s="64"/>
-      <x:c r="K66" s="62"/>
+      <x:c r="K66" s="65"/>
+      <x:c r="L66" s="78"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="61"/>
@@ -1471,7 +1590,8 @@
       <x:c r="H67" s="62"/>
       <x:c r="I67" s="62"/>
       <x:c r="J67" s="64"/>
-      <x:c r="K67" s="62"/>
+      <x:c r="K67" s="65"/>
+      <x:c r="L67" s="78"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="61"/>
@@ -1484,7 +1604,8 @@
       <x:c r="H68" s="62"/>
       <x:c r="I68" s="62"/>
       <x:c r="J68" s="64"/>
-      <x:c r="K68" s="62"/>
+      <x:c r="K68" s="65"/>
+      <x:c r="L68" s="78"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="61"/>
@@ -1497,7 +1618,8 @@
       <x:c r="H69" s="62"/>
       <x:c r="I69" s="62"/>
       <x:c r="J69" s="64"/>
-      <x:c r="K69" s="62"/>
+      <x:c r="K69" s="65"/>
+      <x:c r="L69" s="78"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="61"/>
@@ -1510,7 +1632,8 @@
       <x:c r="H70" s="62"/>
       <x:c r="I70" s="62"/>
       <x:c r="J70" s="64"/>
-      <x:c r="K70" s="62"/>
+      <x:c r="K70" s="65"/>
+      <x:c r="L70" s="78"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="61"/>
@@ -1523,7 +1646,8 @@
       <x:c r="H71" s="62"/>
       <x:c r="I71" s="62"/>
       <x:c r="J71" s="64"/>
-      <x:c r="K71" s="62"/>
+      <x:c r="K71" s="65"/>
+      <x:c r="L71" s="78"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="61"/>
@@ -1536,7 +1660,8 @@
       <x:c r="H72" s="62"/>
       <x:c r="I72" s="62"/>
       <x:c r="J72" s="64"/>
-      <x:c r="K72" s="62"/>
+      <x:c r="K72" s="65"/>
+      <x:c r="L72" s="78"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="61"/>
@@ -1549,7 +1674,8 @@
       <x:c r="H73" s="62"/>
       <x:c r="I73" s="62"/>
       <x:c r="J73" s="64"/>
-      <x:c r="K73" s="62"/>
+      <x:c r="K73" s="65"/>
+      <x:c r="L73" s="78"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="61"/>
@@ -1562,7 +1688,8 @@
       <x:c r="H74" s="62"/>
       <x:c r="I74" s="62"/>
       <x:c r="J74" s="64"/>
-      <x:c r="K74" s="62"/>
+      <x:c r="K74" s="65"/>
+      <x:c r="L74" s="78"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="61"/>
@@ -1575,7 +1702,8 @@
       <x:c r="H75" s="62"/>
       <x:c r="I75" s="62"/>
       <x:c r="J75" s="64"/>
-      <x:c r="K75" s="62"/>
+      <x:c r="K75" s="65"/>
+      <x:c r="L75" s="78"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="61"/>
@@ -1588,7 +1716,8 @@
       <x:c r="H76" s="62"/>
       <x:c r="I76" s="62"/>
       <x:c r="J76" s="64"/>
-      <x:c r="K76" s="62"/>
+      <x:c r="K76" s="65"/>
+      <x:c r="L76" s="78"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="61"/>
@@ -1601,7 +1730,8 @@
       <x:c r="H77" s="62"/>
       <x:c r="I77" s="62"/>
       <x:c r="J77" s="64"/>
-      <x:c r="K77" s="62"/>
+      <x:c r="K77" s="65"/>
+      <x:c r="L77" s="78"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="61"/>
@@ -1614,7 +1744,8 @@
       <x:c r="H78" s="62"/>
       <x:c r="I78" s="62"/>
       <x:c r="J78" s="64"/>
-      <x:c r="K78" s="62"/>
+      <x:c r="K78" s="65"/>
+      <x:c r="L78" s="78"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="61"/>
@@ -1627,7 +1758,8 @@
       <x:c r="H79" s="62"/>
       <x:c r="I79" s="62"/>
       <x:c r="J79" s="64"/>
-      <x:c r="K79" s="62"/>
+      <x:c r="K79" s="65"/>
+      <x:c r="L79" s="78"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="61"/>
@@ -1640,7 +1772,8 @@
       <x:c r="H80" s="62"/>
       <x:c r="I80" s="62"/>
       <x:c r="J80" s="64"/>
-      <x:c r="K80" s="62"/>
+      <x:c r="K80" s="65"/>
+      <x:c r="L80" s="78"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="61"/>
@@ -1653,7 +1786,8 @@
       <x:c r="H81" s="62"/>
       <x:c r="I81" s="62"/>
       <x:c r="J81" s="64"/>
-      <x:c r="K81" s="62"/>
+      <x:c r="K81" s="65"/>
+      <x:c r="L81" s="78"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="61"/>
@@ -1666,7 +1800,8 @@
       <x:c r="H82" s="62"/>
       <x:c r="I82" s="62"/>
       <x:c r="J82" s="64"/>
-      <x:c r="K82" s="62"/>
+      <x:c r="K82" s="65"/>
+      <x:c r="L82" s="78"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="61"/>
@@ -1679,7 +1814,8 @@
       <x:c r="H83" s="62"/>
       <x:c r="I83" s="62"/>
       <x:c r="J83" s="64"/>
-      <x:c r="K83" s="62"/>
+      <x:c r="K83" s="65"/>
+      <x:c r="L83" s="78"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="61"/>
@@ -1692,7 +1828,8 @@
       <x:c r="H84" s="62"/>
       <x:c r="I84" s="62"/>
       <x:c r="J84" s="64"/>
-      <x:c r="K84" s="62"/>
+      <x:c r="K84" s="65"/>
+      <x:c r="L84" s="78"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="61"/>
@@ -1705,7 +1842,8 @@
       <x:c r="H85" s="62"/>
       <x:c r="I85" s="62"/>
       <x:c r="J85" s="64"/>
-      <x:c r="K85" s="62"/>
+      <x:c r="K85" s="65"/>
+      <x:c r="L85" s="78"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="61"/>
@@ -1718,7 +1856,8 @@
       <x:c r="H86" s="62"/>
       <x:c r="I86" s="62"/>
       <x:c r="J86" s="64"/>
-      <x:c r="K86" s="62"/>
+      <x:c r="K86" s="65"/>
+      <x:c r="L86" s="78"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="61"/>
@@ -1731,7 +1870,8 @@
       <x:c r="H87" s="62"/>
       <x:c r="I87" s="62"/>
       <x:c r="J87" s="64"/>
-      <x:c r="K87" s="62"/>
+      <x:c r="K87" s="65"/>
+      <x:c r="L87" s="78"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="61"/>
@@ -1744,7 +1884,8 @@
       <x:c r="H88" s="62"/>
       <x:c r="I88" s="62"/>
       <x:c r="J88" s="64"/>
-      <x:c r="K88" s="62"/>
+      <x:c r="K88" s="65"/>
+      <x:c r="L88" s="78"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="61"/>
@@ -1757,7 +1898,8 @@
       <x:c r="H89" s="62"/>
       <x:c r="I89" s="62"/>
       <x:c r="J89" s="64"/>
-      <x:c r="K89" s="62"/>
+      <x:c r="K89" s="65"/>
+      <x:c r="L89" s="78"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="61"/>
@@ -1770,7 +1912,8 @@
       <x:c r="H90" s="62"/>
       <x:c r="I90" s="62"/>
       <x:c r="J90" s="64"/>
-      <x:c r="K90" s="62"/>
+      <x:c r="K90" s="65"/>
+      <x:c r="L90" s="78"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="61"/>
@@ -1783,7 +1926,8 @@
       <x:c r="H91" s="62"/>
       <x:c r="I91" s="62"/>
       <x:c r="J91" s="64"/>
-      <x:c r="K91" s="62"/>
+      <x:c r="K91" s="65"/>
+      <x:c r="L91" s="78"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="61"/>
@@ -1796,7 +1940,8 @@
       <x:c r="H92" s="62"/>
       <x:c r="I92" s="62"/>
       <x:c r="J92" s="64"/>
-      <x:c r="K92" s="62"/>
+      <x:c r="K92" s="65"/>
+      <x:c r="L92" s="78"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="61"/>
@@ -1809,7 +1954,8 @@
       <x:c r="H93" s="62"/>
       <x:c r="I93" s="62"/>
       <x:c r="J93" s="64"/>
-      <x:c r="K93" s="62"/>
+      <x:c r="K93" s="65"/>
+      <x:c r="L93" s="78"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="61"/>
@@ -1822,7 +1968,8 @@
       <x:c r="H94" s="62"/>
       <x:c r="I94" s="62"/>
       <x:c r="J94" s="64"/>
-      <x:c r="K94" s="62"/>
+      <x:c r="K94" s="65"/>
+      <x:c r="L94" s="78"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="61"/>
@@ -1835,7 +1982,8 @@
       <x:c r="H95" s="62"/>
       <x:c r="I95" s="62"/>
       <x:c r="J95" s="64"/>
-      <x:c r="K95" s="62"/>
+      <x:c r="K95" s="65"/>
+      <x:c r="L95" s="78"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="61"/>
@@ -1848,7 +1996,8 @@
       <x:c r="H96" s="62"/>
       <x:c r="I96" s="62"/>
       <x:c r="J96" s="64"/>
-      <x:c r="K96" s="62"/>
+      <x:c r="K96" s="65"/>
+      <x:c r="L96" s="78"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="61"/>
@@ -1861,7 +2010,8 @@
       <x:c r="H97" s="62"/>
       <x:c r="I97" s="62"/>
       <x:c r="J97" s="64"/>
-      <x:c r="K97" s="62"/>
+      <x:c r="K97" s="65"/>
+      <x:c r="L97" s="78"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="61"/>
@@ -1874,7 +2024,8 @@
       <x:c r="H98" s="62"/>
       <x:c r="I98" s="62"/>
       <x:c r="J98" s="64"/>
-      <x:c r="K98" s="62"/>
+      <x:c r="K98" s="65"/>
+      <x:c r="L98" s="78"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="61"/>
@@ -1887,7 +2038,8 @@
       <x:c r="H99" s="62"/>
       <x:c r="I99" s="62"/>
       <x:c r="J99" s="64"/>
-      <x:c r="K99" s="62"/>
+      <x:c r="K99" s="65"/>
+      <x:c r="L99" s="78"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="61"/>
@@ -1900,7 +2052,8 @@
       <x:c r="H100" s="62"/>
       <x:c r="I100" s="62"/>
       <x:c r="J100" s="64"/>
-      <x:c r="K100" s="62"/>
+      <x:c r="K100" s="65"/>
+      <x:c r="L100" s="78"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="61"/>
@@ -1913,7 +2066,8 @@
       <x:c r="H101" s="62"/>
       <x:c r="I101" s="62"/>
       <x:c r="J101" s="64"/>
-      <x:c r="K101" s="62"/>
+      <x:c r="K101" s="65"/>
+      <x:c r="L101" s="78"/>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="61"/>
@@ -1926,7 +2080,8 @@
       <x:c r="H102" s="62"/>
       <x:c r="I102" s="62"/>
       <x:c r="J102" s="64"/>
-      <x:c r="K102" s="62"/>
+      <x:c r="K102" s="65"/>
+      <x:c r="L102" s="78"/>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="61"/>
@@ -1939,7 +2094,8 @@
       <x:c r="H103" s="62"/>
       <x:c r="I103" s="62"/>
       <x:c r="J103" s="64"/>
-      <x:c r="K103" s="62"/>
+      <x:c r="K103" s="65"/>
+      <x:c r="L103" s="78"/>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="61"/>
@@ -1952,7 +2108,8 @@
       <x:c r="H104" s="62"/>
       <x:c r="I104" s="62"/>
       <x:c r="J104" s="64"/>
-      <x:c r="K104" s="62"/>
+      <x:c r="K104" s="65"/>
+      <x:c r="L104" s="78"/>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="61"/>
@@ -1965,7 +2122,8 @@
       <x:c r="H105" s="62"/>
       <x:c r="I105" s="62"/>
       <x:c r="J105" s="64"/>
-      <x:c r="K105" s="62"/>
+      <x:c r="K105" s="65"/>
+      <x:c r="L105" s="78"/>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="61"/>
@@ -1978,7 +2136,8 @@
       <x:c r="H106" s="62"/>
       <x:c r="I106" s="62"/>
       <x:c r="J106" s="64"/>
-      <x:c r="K106" s="62"/>
+      <x:c r="K106" s="65"/>
+      <x:c r="L106" s="78"/>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="61"/>
@@ -1991,7 +2150,8 @@
       <x:c r="H107" s="62"/>
       <x:c r="I107" s="62"/>
       <x:c r="J107" s="64"/>
-      <x:c r="K107" s="62"/>
+      <x:c r="K107" s="65"/>
+      <x:c r="L107" s="78"/>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="61"/>
@@ -2004,7 +2164,8 @@
       <x:c r="H108" s="62"/>
       <x:c r="I108" s="62"/>
       <x:c r="J108" s="64"/>
-      <x:c r="K108" s="62"/>
+      <x:c r="K108" s="65"/>
+      <x:c r="L108" s="78"/>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="61"/>
@@ -2017,7 +2178,8 @@
       <x:c r="H109" s="62"/>
       <x:c r="I109" s="62"/>
       <x:c r="J109" s="64"/>
-      <x:c r="K109" s="62"/>
+      <x:c r="K109" s="65"/>
+      <x:c r="L109" s="78"/>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="61"/>
@@ -2030,7 +2192,8 @@
       <x:c r="H110" s="62"/>
       <x:c r="I110" s="62"/>
       <x:c r="J110" s="64"/>
-      <x:c r="K110" s="62"/>
+      <x:c r="K110" s="65"/>
+      <x:c r="L110" s="78"/>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="61"/>
@@ -2043,7 +2206,8 @@
       <x:c r="H111" s="62"/>
       <x:c r="I111" s="62"/>
       <x:c r="J111" s="64"/>
-      <x:c r="K111" s="62"/>
+      <x:c r="K111" s="65"/>
+      <x:c r="L111" s="78"/>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="61"/>
@@ -2056,7 +2220,8 @@
       <x:c r="H112" s="62"/>
       <x:c r="I112" s="62"/>
       <x:c r="J112" s="64"/>
-      <x:c r="K112" s="62"/>
+      <x:c r="K112" s="65"/>
+      <x:c r="L112" s="78"/>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="61"/>
@@ -2069,7 +2234,8 @@
       <x:c r="H113" s="62"/>
       <x:c r="I113" s="62"/>
       <x:c r="J113" s="64"/>
-      <x:c r="K113" s="62"/>
+      <x:c r="K113" s="65"/>
+      <x:c r="L113" s="78"/>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="61"/>
@@ -2082,7 +2248,8 @@
       <x:c r="H114" s="62"/>
       <x:c r="I114" s="62"/>
       <x:c r="J114" s="64"/>
-      <x:c r="K114" s="62"/>
+      <x:c r="K114" s="65"/>
+      <x:c r="L114" s="78"/>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="61"/>
@@ -2095,7 +2262,8 @@
       <x:c r="H115" s="62"/>
       <x:c r="I115" s="62"/>
       <x:c r="J115" s="64"/>
-      <x:c r="K115" s="62"/>
+      <x:c r="K115" s="65"/>
+      <x:c r="L115" s="78"/>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="61"/>
@@ -2108,7 +2276,8 @@
       <x:c r="H116" s="62"/>
       <x:c r="I116" s="62"/>
       <x:c r="J116" s="64"/>
-      <x:c r="K116" s="62"/>
+      <x:c r="K116" s="65"/>
+      <x:c r="L116" s="78"/>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="61"/>
@@ -2121,7 +2290,8 @@
       <x:c r="H117" s="62"/>
       <x:c r="I117" s="62"/>
       <x:c r="J117" s="64"/>
-      <x:c r="K117" s="62"/>
+      <x:c r="K117" s="65"/>
+      <x:c r="L117" s="78"/>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="61"/>
@@ -2134,7 +2304,8 @@
       <x:c r="H118" s="62"/>
       <x:c r="I118" s="62"/>
       <x:c r="J118" s="64"/>
-      <x:c r="K118" s="62"/>
+      <x:c r="K118" s="65"/>
+      <x:c r="L118" s="78"/>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="61"/>
@@ -2147,7 +2318,8 @@
       <x:c r="H119" s="62"/>
       <x:c r="I119" s="62"/>
       <x:c r="J119" s="64"/>
-      <x:c r="K119" s="62"/>
+      <x:c r="K119" s="65"/>
+      <x:c r="L119" s="78"/>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="61"/>
@@ -2160,7 +2332,8 @@
       <x:c r="H120" s="62"/>
       <x:c r="I120" s="62"/>
       <x:c r="J120" s="64"/>
-      <x:c r="K120" s="62"/>
+      <x:c r="K120" s="65"/>
+      <x:c r="L120" s="78"/>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="61"/>
@@ -2173,7 +2346,8 @@
       <x:c r="H121" s="62"/>
       <x:c r="I121" s="62"/>
       <x:c r="J121" s="64"/>
-      <x:c r="K121" s="62"/>
+      <x:c r="K121" s="65"/>
+      <x:c r="L121" s="78"/>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="61"/>
@@ -2186,7 +2360,8 @@
       <x:c r="H122" s="62"/>
       <x:c r="I122" s="62"/>
       <x:c r="J122" s="64"/>
-      <x:c r="K122" s="62"/>
+      <x:c r="K122" s="65"/>
+      <x:c r="L122" s="78"/>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="61"/>
@@ -2199,7 +2374,8 @@
       <x:c r="H123" s="62"/>
       <x:c r="I123" s="62"/>
       <x:c r="J123" s="64"/>
-      <x:c r="K123" s="62"/>
+      <x:c r="K123" s="65"/>
+      <x:c r="L123" s="78"/>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="61"/>
@@ -2212,7 +2388,8 @@
       <x:c r="H124" s="62"/>
       <x:c r="I124" s="62"/>
       <x:c r="J124" s="64"/>
-      <x:c r="K124" s="62"/>
+      <x:c r="K124" s="65"/>
+      <x:c r="L124" s="78"/>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="61"/>
@@ -2225,7 +2402,8 @@
       <x:c r="H125" s="62"/>
       <x:c r="I125" s="62"/>
       <x:c r="J125" s="64"/>
-      <x:c r="K125" s="62"/>
+      <x:c r="K125" s="65"/>
+      <x:c r="L125" s="78"/>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="61"/>
@@ -2238,7 +2416,8 @@
       <x:c r="H126" s="62"/>
       <x:c r="I126" s="62"/>
       <x:c r="J126" s="64"/>
-      <x:c r="K126" s="62"/>
+      <x:c r="K126" s="65"/>
+      <x:c r="L126" s="78"/>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="61"/>
@@ -2251,7 +2430,8 @@
       <x:c r="H127" s="62"/>
       <x:c r="I127" s="62"/>
       <x:c r="J127" s="64"/>
-      <x:c r="K127" s="62"/>
+      <x:c r="K127" s="65"/>
+      <x:c r="L127" s="78"/>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="61"/>
@@ -2264,7 +2444,8 @@
       <x:c r="H128" s="62"/>
       <x:c r="I128" s="62"/>
       <x:c r="J128" s="64"/>
-      <x:c r="K128" s="62"/>
+      <x:c r="K128" s="65"/>
+      <x:c r="L128" s="78"/>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="61"/>
@@ -2277,7 +2458,8 @@
       <x:c r="H129" s="62"/>
       <x:c r="I129" s="62"/>
       <x:c r="J129" s="64"/>
-      <x:c r="K129" s="62"/>
+      <x:c r="K129" s="65"/>
+      <x:c r="L129" s="78"/>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="61"/>
@@ -2290,7 +2472,8 @@
       <x:c r="H130" s="62"/>
       <x:c r="I130" s="62"/>
       <x:c r="J130" s="64"/>
-      <x:c r="K130" s="62"/>
+      <x:c r="K130" s="65"/>
+      <x:c r="L130" s="78"/>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="61"/>
@@ -2303,7 +2486,8 @@
       <x:c r="H131" s="62"/>
       <x:c r="I131" s="62"/>
       <x:c r="J131" s="64"/>
-      <x:c r="K131" s="62"/>
+      <x:c r="K131" s="65"/>
+      <x:c r="L131" s="78"/>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="61"/>
@@ -2316,7 +2500,8 @@
       <x:c r="H132" s="62"/>
       <x:c r="I132" s="62"/>
       <x:c r="J132" s="64"/>
-      <x:c r="K132" s="62"/>
+      <x:c r="K132" s="65"/>
+      <x:c r="L132" s="78"/>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="61"/>
@@ -2329,7 +2514,8 @@
       <x:c r="H133" s="62"/>
       <x:c r="I133" s="62"/>
       <x:c r="J133" s="64"/>
-      <x:c r="K133" s="62"/>
+      <x:c r="K133" s="65"/>
+      <x:c r="L133" s="78"/>
     </x:row>
     <x:row r="134">
       <x:c r="A134" s="61"/>
@@ -2342,7 +2528,8 @@
       <x:c r="H134" s="62"/>
       <x:c r="I134" s="62"/>
       <x:c r="J134" s="64"/>
-      <x:c r="K134" s="62"/>
+      <x:c r="K134" s="65"/>
+      <x:c r="L134" s="78"/>
     </x:row>
     <x:row r="135">
       <x:c r="A135" s="61"/>
@@ -2355,7 +2542,8 @@
       <x:c r="H135" s="62"/>
       <x:c r="I135" s="62"/>
       <x:c r="J135" s="64"/>
-      <x:c r="K135" s="62"/>
+      <x:c r="K135" s="65"/>
+      <x:c r="L135" s="78"/>
     </x:row>
     <x:row r="136">
       <x:c r="A136" s="61"/>
@@ -2368,7 +2556,8 @@
       <x:c r="H136" s="62"/>
       <x:c r="I136" s="62"/>
       <x:c r="J136" s="64"/>
-      <x:c r="K136" s="62"/>
+      <x:c r="K136" s="65"/>
+      <x:c r="L136" s="78"/>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="61"/>
@@ -2381,7 +2570,8 @@
       <x:c r="H137" s="62"/>
       <x:c r="I137" s="62"/>
       <x:c r="J137" s="64"/>
-      <x:c r="K137" s="62"/>
+      <x:c r="K137" s="65"/>
+      <x:c r="L137" s="78"/>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="61"/>
@@ -2394,7 +2584,8 @@
       <x:c r="H138" s="62"/>
       <x:c r="I138" s="62"/>
       <x:c r="J138" s="64"/>
-      <x:c r="K138" s="62"/>
+      <x:c r="K138" s="65"/>
+      <x:c r="L138" s="78"/>
     </x:row>
     <x:row r="139">
       <x:c r="A139" s="61"/>
@@ -2407,7 +2598,8 @@
       <x:c r="H139" s="62"/>
       <x:c r="I139" s="62"/>
       <x:c r="J139" s="64"/>
-      <x:c r="K139" s="62"/>
+      <x:c r="K139" s="65"/>
+      <x:c r="L139" s="78"/>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="61"/>
@@ -2420,7 +2612,8 @@
       <x:c r="H140" s="62"/>
       <x:c r="I140" s="62"/>
       <x:c r="J140" s="64"/>
-      <x:c r="K140" s="62"/>
+      <x:c r="K140" s="65"/>
+      <x:c r="L140" s="78"/>
     </x:row>
     <x:row r="141">
       <x:c r="A141" s="61"/>
@@ -2433,7 +2626,8 @@
       <x:c r="H141" s="62"/>
       <x:c r="I141" s="62"/>
       <x:c r="J141" s="64"/>
-      <x:c r="K141" s="62"/>
+      <x:c r="K141" s="65"/>
+      <x:c r="L141" s="78"/>
     </x:row>
     <x:row r="142">
       <x:c r="A142" s="61"/>
@@ -2446,7 +2640,8 @@
       <x:c r="H142" s="62"/>
       <x:c r="I142" s="62"/>
       <x:c r="J142" s="64"/>
-      <x:c r="K142" s="62"/>
+      <x:c r="K142" s="65"/>
+      <x:c r="L142" s="78"/>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="61"/>
@@ -2459,7 +2654,8 @@
       <x:c r="H143" s="62"/>
       <x:c r="I143" s="62"/>
       <x:c r="J143" s="64"/>
-      <x:c r="K143" s="62"/>
+      <x:c r="K143" s="65"/>
+      <x:c r="L143" s="78"/>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="61"/>
@@ -2472,7 +2668,8 @@
       <x:c r="H144" s="62"/>
       <x:c r="I144" s="62"/>
       <x:c r="J144" s="64"/>
-      <x:c r="K144" s="62"/>
+      <x:c r="K144" s="65"/>
+      <x:c r="L144" s="78"/>
     </x:row>
     <x:row r="145">
       <x:c r="A145" s="61"/>
@@ -2485,7 +2682,8 @@
       <x:c r="H145" s="62"/>
       <x:c r="I145" s="62"/>
       <x:c r="J145" s="64"/>
-      <x:c r="K145" s="62"/>
+      <x:c r="K145" s="65"/>
+      <x:c r="L145" s="78"/>
     </x:row>
     <x:row r="146">
       <x:c r="A146" s="61"/>
@@ -2498,7 +2696,8 @@
       <x:c r="H146" s="62"/>
       <x:c r="I146" s="62"/>
       <x:c r="J146" s="64"/>
-      <x:c r="K146" s="62"/>
+      <x:c r="K146" s="65"/>
+      <x:c r="L146" s="78"/>
     </x:row>
     <x:row r="147">
       <x:c r="A147" s="61"/>
@@ -2511,7 +2710,8 @@
       <x:c r="H147" s="62"/>
       <x:c r="I147" s="62"/>
       <x:c r="J147" s="64"/>
-      <x:c r="K147" s="62"/>
+      <x:c r="K147" s="65"/>
+      <x:c r="L147" s="78"/>
     </x:row>
     <x:row r="148">
       <x:c r="A148" s="61"/>
@@ -2524,7 +2724,8 @@
       <x:c r="H148" s="62"/>
       <x:c r="I148" s="62"/>
       <x:c r="J148" s="64"/>
-      <x:c r="K148" s="62"/>
+      <x:c r="K148" s="65"/>
+      <x:c r="L148" s="78"/>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="61"/>
@@ -2537,7 +2738,8 @@
       <x:c r="H149" s="62"/>
       <x:c r="I149" s="62"/>
       <x:c r="J149" s="64"/>
-      <x:c r="K149" s="62"/>
+      <x:c r="K149" s="65"/>
+      <x:c r="L149" s="78"/>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="61"/>
@@ -2550,7 +2752,8 @@
       <x:c r="H150" s="62"/>
       <x:c r="I150" s="62"/>
       <x:c r="J150" s="64"/>
-      <x:c r="K150" s="62"/>
+      <x:c r="K150" s="65"/>
+      <x:c r="L150" s="78"/>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="61"/>
@@ -2563,7 +2766,8 @@
       <x:c r="H151" s="62"/>
       <x:c r="I151" s="62"/>
       <x:c r="J151" s="64"/>
-      <x:c r="K151" s="62"/>
+      <x:c r="K151" s="65"/>
+      <x:c r="L151" s="78"/>
     </x:row>
     <x:row r="152">
       <x:c r="A152" s="61"/>
@@ -2576,7 +2780,8 @@
       <x:c r="H152" s="62"/>
       <x:c r="I152" s="62"/>
       <x:c r="J152" s="64"/>
-      <x:c r="K152" s="62"/>
+      <x:c r="K152" s="65"/>
+      <x:c r="L152" s="78"/>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="61"/>
@@ -2589,7 +2794,8 @@
       <x:c r="H153" s="62"/>
       <x:c r="I153" s="62"/>
       <x:c r="J153" s="64"/>
-      <x:c r="K153" s="62"/>
+      <x:c r="K153" s="65"/>
+      <x:c r="L153" s="78"/>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="61"/>
@@ -2602,7 +2808,8 @@
       <x:c r="H154" s="62"/>
       <x:c r="I154" s="62"/>
       <x:c r="J154" s="64"/>
-      <x:c r="K154" s="62"/>
+      <x:c r="K154" s="65"/>
+      <x:c r="L154" s="78"/>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="61"/>
@@ -2615,7 +2822,8 @@
       <x:c r="H155" s="62"/>
       <x:c r="I155" s="62"/>
       <x:c r="J155" s="64"/>
-      <x:c r="K155" s="62"/>
+      <x:c r="K155" s="65"/>
+      <x:c r="L155" s="78"/>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="61"/>
@@ -2628,7 +2836,8 @@
       <x:c r="H156" s="62"/>
       <x:c r="I156" s="62"/>
       <x:c r="J156" s="64"/>
-      <x:c r="K156" s="62"/>
+      <x:c r="K156" s="65"/>
+      <x:c r="L156" s="78"/>
     </x:row>
     <x:row r="157">
       <x:c r="A157" s="61"/>
@@ -2641,7 +2850,8 @@
       <x:c r="H157" s="62"/>
       <x:c r="I157" s="62"/>
       <x:c r="J157" s="64"/>
-      <x:c r="K157" s="62"/>
+      <x:c r="K157" s="65"/>
+      <x:c r="L157" s="78"/>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="61"/>
@@ -2654,7 +2864,8 @@
       <x:c r="H158" s="62"/>
       <x:c r="I158" s="62"/>
       <x:c r="J158" s="64"/>
-      <x:c r="K158" s="62"/>
+      <x:c r="K158" s="65"/>
+      <x:c r="L158" s="78"/>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="61"/>
@@ -2667,7 +2878,8 @@
       <x:c r="H159" s="62"/>
       <x:c r="I159" s="62"/>
       <x:c r="J159" s="64"/>
-      <x:c r="K159" s="62"/>
+      <x:c r="K159" s="65"/>
+      <x:c r="L159" s="78"/>
     </x:row>
     <x:row r="160">
       <x:c r="A160" s="61"/>
@@ -2680,7 +2892,8 @@
       <x:c r="H160" s="62"/>
       <x:c r="I160" s="62"/>
       <x:c r="J160" s="64"/>
-      <x:c r="K160" s="62"/>
+      <x:c r="K160" s="65"/>
+      <x:c r="L160" s="78"/>
     </x:row>
     <x:row r="161">
       <x:c r="A161" s="61"/>
@@ -2693,7 +2906,8 @@
       <x:c r="H161" s="62"/>
       <x:c r="I161" s="62"/>
       <x:c r="J161" s="64"/>
-      <x:c r="K161" s="62"/>
+      <x:c r="K161" s="65"/>
+      <x:c r="L161" s="78"/>
     </x:row>
     <x:row r="162">
       <x:c r="A162" s="61"/>
@@ -2706,7 +2920,8 @@
       <x:c r="H162" s="62"/>
       <x:c r="I162" s="62"/>
       <x:c r="J162" s="64"/>
-      <x:c r="K162" s="62"/>
+      <x:c r="K162" s="65"/>
+      <x:c r="L162" s="78"/>
     </x:row>
     <x:row r="163">
       <x:c r="A163" s="61"/>
@@ -2719,7 +2934,8 @@
       <x:c r="H163" s="62"/>
       <x:c r="I163" s="62"/>
       <x:c r="J163" s="64"/>
-      <x:c r="K163" s="62"/>
+      <x:c r="K163" s="65"/>
+      <x:c r="L163" s="78"/>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="61"/>
@@ -2732,7 +2948,8 @@
       <x:c r="H164" s="62"/>
       <x:c r="I164" s="62"/>
       <x:c r="J164" s="64"/>
-      <x:c r="K164" s="62"/>
+      <x:c r="K164" s="65"/>
+      <x:c r="L164" s="78"/>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="61"/>
@@ -2745,7 +2962,8 @@
       <x:c r="H165" s="62"/>
       <x:c r="I165" s="62"/>
       <x:c r="J165" s="64"/>
-      <x:c r="K165" s="62"/>
+      <x:c r="K165" s="65"/>
+      <x:c r="L165" s="78"/>
     </x:row>
     <x:row r="166">
       <x:c r="A166" s="61"/>
@@ -2758,7 +2976,8 @@
       <x:c r="H166" s="62"/>
       <x:c r="I166" s="62"/>
       <x:c r="J166" s="64"/>
-      <x:c r="K166" s="62"/>
+      <x:c r="K166" s="65"/>
+      <x:c r="L166" s="78"/>
     </x:row>
     <x:row r="167">
       <x:c r="A167" s="61"/>
@@ -2771,7 +2990,8 @@
       <x:c r="H167" s="62"/>
       <x:c r="I167" s="62"/>
       <x:c r="J167" s="64"/>
-      <x:c r="K167" s="62"/>
+      <x:c r="K167" s="65"/>
+      <x:c r="L167" s="78"/>
     </x:row>
     <x:row r="168">
       <x:c r="A168" s="61"/>
@@ -2784,7 +3004,8 @@
       <x:c r="H168" s="62"/>
       <x:c r="I168" s="62"/>
       <x:c r="J168" s="64"/>
-      <x:c r="K168" s="62"/>
+      <x:c r="K168" s="65"/>
+      <x:c r="L168" s="78"/>
     </x:row>
     <x:row r="169">
       <x:c r="A169" s="61"/>
@@ -2797,7 +3018,8 @@
       <x:c r="H169" s="62"/>
       <x:c r="I169" s="62"/>
       <x:c r="J169" s="64"/>
-      <x:c r="K169" s="62"/>
+      <x:c r="K169" s="65"/>
+      <x:c r="L169" s="78"/>
     </x:row>
     <x:row r="170">
       <x:c r="A170" s="61"/>
@@ -2810,7 +3032,8 @@
       <x:c r="H170" s="62"/>
       <x:c r="I170" s="62"/>
       <x:c r="J170" s="64"/>
-      <x:c r="K170" s="62"/>
+      <x:c r="K170" s="65"/>
+      <x:c r="L170" s="78"/>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="61"/>
@@ -2823,7 +3046,8 @@
       <x:c r="H171" s="62"/>
       <x:c r="I171" s="62"/>
       <x:c r="J171" s="64"/>
-      <x:c r="K171" s="62"/>
+      <x:c r="K171" s="65"/>
+      <x:c r="L171" s="78"/>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="61"/>
@@ -2836,7 +3060,8 @@
       <x:c r="H172" s="62"/>
       <x:c r="I172" s="62"/>
       <x:c r="J172" s="64"/>
-      <x:c r="K172" s="62"/>
+      <x:c r="K172" s="65"/>
+      <x:c r="L172" s="78"/>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="61"/>
@@ -2849,7 +3074,8 @@
       <x:c r="H173" s="62"/>
       <x:c r="I173" s="62"/>
       <x:c r="J173" s="64"/>
-      <x:c r="K173" s="62"/>
+      <x:c r="K173" s="65"/>
+      <x:c r="L173" s="78"/>
     </x:row>
     <x:row r="174">
       <x:c r="A174" s="61"/>
@@ -2862,7 +3088,8 @@
       <x:c r="H174" s="62"/>
       <x:c r="I174" s="62"/>
       <x:c r="J174" s="64"/>
-      <x:c r="K174" s="62"/>
+      <x:c r="K174" s="65"/>
+      <x:c r="L174" s="78"/>
     </x:row>
     <x:row r="175">
       <x:c r="A175" s="61"/>
@@ -2875,7 +3102,8 @@
       <x:c r="H175" s="62"/>
       <x:c r="I175" s="62"/>
       <x:c r="J175" s="64"/>
-      <x:c r="K175" s="62"/>
+      <x:c r="K175" s="65"/>
+      <x:c r="L175" s="78"/>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="61"/>
@@ -2888,7 +3116,8 @@
       <x:c r="H176" s="62"/>
       <x:c r="I176" s="62"/>
       <x:c r="J176" s="64"/>
-      <x:c r="K176" s="62"/>
+      <x:c r="K176" s="65"/>
+      <x:c r="L176" s="78"/>
     </x:row>
     <x:row r="177">
       <x:c r="A177" s="61"/>
@@ -2901,7 +3130,8 @@
       <x:c r="H177" s="62"/>
       <x:c r="I177" s="62"/>
       <x:c r="J177" s="64"/>
-      <x:c r="K177" s="62"/>
+      <x:c r="K177" s="65"/>
+      <x:c r="L177" s="78"/>
     </x:row>
     <x:row r="178">
       <x:c r="A178" s="61"/>
@@ -2914,7 +3144,8 @@
       <x:c r="H178" s="62"/>
       <x:c r="I178" s="62"/>
       <x:c r="J178" s="64"/>
-      <x:c r="K178" s="62"/>
+      <x:c r="K178" s="65"/>
+      <x:c r="L178" s="78"/>
     </x:row>
     <x:row r="179">
       <x:c r="A179" s="61"/>
@@ -2927,7 +3158,8 @@
       <x:c r="H179" s="62"/>
       <x:c r="I179" s="62"/>
       <x:c r="J179" s="64"/>
-      <x:c r="K179" s="62"/>
+      <x:c r="K179" s="65"/>
+      <x:c r="L179" s="78"/>
     </x:row>
     <x:row r="180">
       <x:c r="A180" s="61"/>
@@ -2940,7 +3172,8 @@
       <x:c r="H180" s="62"/>
       <x:c r="I180" s="62"/>
       <x:c r="J180" s="64"/>
-      <x:c r="K180" s="62"/>
+      <x:c r="K180" s="65"/>
+      <x:c r="L180" s="78"/>
     </x:row>
     <x:row r="181">
       <x:c r="A181" s="61"/>
@@ -2953,7 +3186,8 @@
       <x:c r="H181" s="62"/>
       <x:c r="I181" s="62"/>
       <x:c r="J181" s="64"/>
-      <x:c r="K181" s="62"/>
+      <x:c r="K181" s="65"/>
+      <x:c r="L181" s="78"/>
     </x:row>
     <x:row r="182">
       <x:c r="A182" s="61"/>
@@ -2966,7 +3200,8 @@
       <x:c r="H182" s="62"/>
       <x:c r="I182" s="62"/>
       <x:c r="J182" s="64"/>
-      <x:c r="K182" s="62"/>
+      <x:c r="K182" s="65"/>
+      <x:c r="L182" s="78"/>
     </x:row>
     <x:row r="183">
       <x:c r="A183" s="61"/>
@@ -2979,7 +3214,8 @@
       <x:c r="H183" s="62"/>
       <x:c r="I183" s="62"/>
       <x:c r="J183" s="64"/>
-      <x:c r="K183" s="62"/>
+      <x:c r="K183" s="65"/>
+      <x:c r="L183" s="78"/>
     </x:row>
     <x:row r="184">
       <x:c r="A184" s="61"/>
@@ -2992,7 +3228,8 @@
       <x:c r="H184" s="62"/>
       <x:c r="I184" s="62"/>
       <x:c r="J184" s="64"/>
-      <x:c r="K184" s="62"/>
+      <x:c r="K184" s="65"/>
+      <x:c r="L184" s="78"/>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="61"/>
@@ -3005,7 +3242,8 @@
       <x:c r="H185" s="62"/>
       <x:c r="I185" s="62"/>
       <x:c r="J185" s="64"/>
-      <x:c r="K185" s="62"/>
+      <x:c r="K185" s="65"/>
+      <x:c r="L185" s="78"/>
     </x:row>
     <x:row r="186">
       <x:c r="A186" s="61"/>
@@ -3018,7 +3256,8 @@
       <x:c r="H186" s="62"/>
       <x:c r="I186" s="62"/>
       <x:c r="J186" s="64"/>
-      <x:c r="K186" s="62"/>
+      <x:c r="K186" s="65"/>
+      <x:c r="L186" s="78"/>
     </x:row>
     <x:row r="187">
       <x:c r="A187" s="61"/>
@@ -3031,7 +3270,8 @@
       <x:c r="H187" s="62"/>
       <x:c r="I187" s="62"/>
       <x:c r="J187" s="64"/>
-      <x:c r="K187" s="62"/>
+      <x:c r="K187" s="65"/>
+      <x:c r="L187" s="78"/>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="61"/>
@@ -3044,7 +3284,8 @@
       <x:c r="H188" s="62"/>
       <x:c r="I188" s="62"/>
       <x:c r="J188" s="64"/>
-      <x:c r="K188" s="62"/>
+      <x:c r="K188" s="65"/>
+      <x:c r="L188" s="78"/>
     </x:row>
     <x:row r="189">
       <x:c r="A189" s="61"/>
@@ -3057,7 +3298,8 @@
       <x:c r="H189" s="62"/>
       <x:c r="I189" s="62"/>
       <x:c r="J189" s="64"/>
-      <x:c r="K189" s="62"/>
+      <x:c r="K189" s="65"/>
+      <x:c r="L189" s="78"/>
     </x:row>
     <x:row r="190">
       <x:c r="A190" s="61"/>
@@ -3070,7 +3312,8 @@
       <x:c r="H190" s="62"/>
       <x:c r="I190" s="62"/>
       <x:c r="J190" s="64"/>
-      <x:c r="K190" s="62"/>
+      <x:c r="K190" s="65"/>
+      <x:c r="L190" s="78"/>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="61"/>
@@ -3083,7 +3326,8 @@
       <x:c r="H191" s="62"/>
       <x:c r="I191" s="62"/>
       <x:c r="J191" s="64"/>
-      <x:c r="K191" s="62"/>
+      <x:c r="K191" s="65"/>
+      <x:c r="L191" s="78"/>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="61"/>
@@ -3096,7 +3340,8 @@
       <x:c r="H192" s="62"/>
       <x:c r="I192" s="62"/>
       <x:c r="J192" s="64"/>
-      <x:c r="K192" s="62"/>
+      <x:c r="K192" s="65"/>
+      <x:c r="L192" s="78"/>
     </x:row>
     <x:row r="193">
       <x:c r="A193" s="61"/>
@@ -3109,7 +3354,8 @@
       <x:c r="H193" s="62"/>
       <x:c r="I193" s="62"/>
       <x:c r="J193" s="64"/>
-      <x:c r="K193" s="62"/>
+      <x:c r="K193" s="65"/>
+      <x:c r="L193" s="78"/>
     </x:row>
     <x:row r="194">
       <x:c r="A194" s="61"/>
@@ -3122,7 +3368,8 @@
       <x:c r="H194" s="62"/>
       <x:c r="I194" s="62"/>
       <x:c r="J194" s="64"/>
-      <x:c r="K194" s="62"/>
+      <x:c r="K194" s="65"/>
+      <x:c r="L194" s="78"/>
     </x:row>
     <x:row r="195">
       <x:c r="A195" s="61"/>
@@ -3135,7 +3382,8 @@
       <x:c r="H195" s="62"/>
       <x:c r="I195" s="62"/>
       <x:c r="J195" s="64"/>
-      <x:c r="K195" s="62"/>
+      <x:c r="K195" s="65"/>
+      <x:c r="L195" s="78"/>
     </x:row>
     <x:row r="196">
       <x:c r="A196" s="61"/>
@@ -3148,7 +3396,8 @@
       <x:c r="H196" s="62"/>
       <x:c r="I196" s="62"/>
       <x:c r="J196" s="64"/>
-      <x:c r="K196" s="62"/>
+      <x:c r="K196" s="65"/>
+      <x:c r="L196" s="78"/>
     </x:row>
     <x:row r="197">
       <x:c r="A197" s="61"/>
@@ -3161,7 +3410,8 @@
       <x:c r="H197" s="62"/>
       <x:c r="I197" s="62"/>
       <x:c r="J197" s="64"/>
-      <x:c r="K197" s="62"/>
+      <x:c r="K197" s="65"/>
+      <x:c r="L197" s="78"/>
     </x:row>
     <x:row r="198">
       <x:c r="A198" s="61"/>
@@ -3174,7 +3424,8 @@
       <x:c r="H198" s="62"/>
       <x:c r="I198" s="62"/>
       <x:c r="J198" s="64"/>
-      <x:c r="K198" s="62"/>
+      <x:c r="K198" s="65"/>
+      <x:c r="L198" s="78"/>
     </x:row>
     <x:row r="199">
       <x:c r="A199" s="61"/>
@@ -3187,7 +3438,8 @@
       <x:c r="H199" s="62"/>
       <x:c r="I199" s="62"/>
       <x:c r="J199" s="64"/>
-      <x:c r="K199" s="62"/>
+      <x:c r="K199" s="65"/>
+      <x:c r="L199" s="78"/>
     </x:row>
     <x:row r="200">
       <x:c r="A200" s="61"/>
@@ -3200,7 +3452,8 @@
       <x:c r="H200" s="62"/>
       <x:c r="I200" s="62"/>
       <x:c r="J200" s="64"/>
-      <x:c r="K200" s="62"/>
+      <x:c r="K200" s="65"/>
+      <x:c r="L200" s="78"/>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="61"/>
@@ -3213,7 +3466,8 @@
       <x:c r="H201" s="62"/>
       <x:c r="I201" s="62"/>
       <x:c r="J201" s="64"/>
-      <x:c r="K201" s="62"/>
+      <x:c r="K201" s="65"/>
+      <x:c r="L201" s="78"/>
     </x:row>
     <x:row r="202">
       <x:c r="A202" s="61"/>
@@ -3226,7 +3480,8 @@
       <x:c r="H202" s="62"/>
       <x:c r="I202" s="62"/>
       <x:c r="J202" s="64"/>
-      <x:c r="K202" s="62"/>
+      <x:c r="K202" s="65"/>
+      <x:c r="L202" s="78"/>
     </x:row>
     <x:row r="203">
       <x:c r="A203" s="61"/>
@@ -3239,7 +3494,8 @@
       <x:c r="H203" s="62"/>
       <x:c r="I203" s="62"/>
       <x:c r="J203" s="64"/>
-      <x:c r="K203" s="62"/>
+      <x:c r="K203" s="65"/>
+      <x:c r="L203" s="78"/>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="61"/>
@@ -3252,7 +3508,8 @@
       <x:c r="H204" s="62"/>
       <x:c r="I204" s="62"/>
       <x:c r="J204" s="64"/>
-      <x:c r="K204" s="62"/>
+      <x:c r="K204" s="65"/>
+      <x:c r="L204" s="78"/>
     </x:row>
     <x:row r="205">
       <x:c r="A205" s="61"/>
@@ -3265,7 +3522,8 @@
       <x:c r="H205" s="62"/>
       <x:c r="I205" s="62"/>
       <x:c r="J205" s="64"/>
-      <x:c r="K205" s="62"/>
+      <x:c r="K205" s="65"/>
+      <x:c r="L205" s="78"/>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="61"/>
@@ -3278,7 +3536,8 @@
       <x:c r="H206" s="62"/>
       <x:c r="I206" s="62"/>
       <x:c r="J206" s="64"/>
-      <x:c r="K206" s="62"/>
+      <x:c r="K206" s="65"/>
+      <x:c r="L206" s="78"/>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="61"/>
@@ -3291,7 +3550,8 @@
       <x:c r="H207" s="62"/>
       <x:c r="I207" s="62"/>
       <x:c r="J207" s="64"/>
-      <x:c r="K207" s="62"/>
+      <x:c r="K207" s="65"/>
+      <x:c r="L207" s="78"/>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="61"/>
@@ -3304,7 +3564,8 @@
       <x:c r="H208" s="62"/>
       <x:c r="I208" s="62"/>
       <x:c r="J208" s="64"/>
-      <x:c r="K208" s="62"/>
+      <x:c r="K208" s="65"/>
+      <x:c r="L208" s="78"/>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="61"/>
@@ -3317,7 +3578,8 @@
       <x:c r="H209" s="62"/>
       <x:c r="I209" s="62"/>
       <x:c r="J209" s="64"/>
-      <x:c r="K209" s="62"/>
+      <x:c r="K209" s="65"/>
+      <x:c r="L209" s="78"/>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="61"/>
@@ -3330,7 +3592,8 @@
       <x:c r="H210" s="62"/>
       <x:c r="I210" s="62"/>
       <x:c r="J210" s="64"/>
-      <x:c r="K210" s="62"/>
+      <x:c r="K210" s="65"/>
+      <x:c r="L210" s="78"/>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="61"/>
@@ -3343,7 +3606,8 @@
       <x:c r="H211" s="62"/>
       <x:c r="I211" s="62"/>
       <x:c r="J211" s="64"/>
-      <x:c r="K211" s="62"/>
+      <x:c r="K211" s="65"/>
+      <x:c r="L211" s="78"/>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="61"/>
@@ -3356,7 +3620,8 @@
       <x:c r="H212" s="62"/>
       <x:c r="I212" s="62"/>
       <x:c r="J212" s="64"/>
-      <x:c r="K212" s="62"/>
+      <x:c r="K212" s="65"/>
+      <x:c r="L212" s="78"/>
     </x:row>
     <x:row r="213">
       <x:c r="A213" s="61"/>
@@ -3369,7 +3634,8 @@
       <x:c r="H213" s="62"/>
       <x:c r="I213" s="62"/>
       <x:c r="J213" s="64"/>
-      <x:c r="K213" s="62"/>
+      <x:c r="K213" s="65"/>
+      <x:c r="L213" s="78"/>
     </x:row>
     <x:row r="214">
       <x:c r="A214" s="61"/>
@@ -3382,7 +3648,8 @@
       <x:c r="H214" s="62"/>
       <x:c r="I214" s="62"/>
       <x:c r="J214" s="64"/>
-      <x:c r="K214" s="62"/>
+      <x:c r="K214" s="65"/>
+      <x:c r="L214" s="78"/>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="61"/>
@@ -3395,7 +3662,8 @@
       <x:c r="H215" s="62"/>
       <x:c r="I215" s="62"/>
       <x:c r="J215" s="64"/>
-      <x:c r="K215" s="62"/>
+      <x:c r="K215" s="65"/>
+      <x:c r="L215" s="78"/>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="61"/>
@@ -3408,7 +3676,8 @@
       <x:c r="H216" s="62"/>
       <x:c r="I216" s="62"/>
       <x:c r="J216" s="64"/>
-      <x:c r="K216" s="62"/>
+      <x:c r="K216" s="65"/>
+      <x:c r="L216" s="78"/>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="61"/>
@@ -3421,7 +3690,8 @@
       <x:c r="H217" s="62"/>
       <x:c r="I217" s="62"/>
       <x:c r="J217" s="64"/>
-      <x:c r="K217" s="62"/>
+      <x:c r="K217" s="65"/>
+      <x:c r="L217" s="78"/>
     </x:row>
     <x:row r="218">
       <x:c r="A218" s="61"/>
@@ -3434,7 +3704,8 @@
       <x:c r="H218" s="62"/>
       <x:c r="I218" s="62"/>
       <x:c r="J218" s="64"/>
-      <x:c r="K218" s="62"/>
+      <x:c r="K218" s="65"/>
+      <x:c r="L218" s="78"/>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="61"/>
@@ -3447,7 +3718,8 @@
       <x:c r="H219" s="62"/>
       <x:c r="I219" s="62"/>
       <x:c r="J219" s="64"/>
-      <x:c r="K219" s="62"/>
+      <x:c r="K219" s="65"/>
+      <x:c r="L219" s="78"/>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="61"/>
@@ -3460,7 +3732,8 @@
       <x:c r="H220" s="62"/>
       <x:c r="I220" s="62"/>
       <x:c r="J220" s="64"/>
-      <x:c r="K220" s="62"/>
+      <x:c r="K220" s="65"/>
+      <x:c r="L220" s="78"/>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="61"/>
@@ -3473,7 +3746,8 @@
       <x:c r="H221" s="62"/>
       <x:c r="I221" s="62"/>
       <x:c r="J221" s="64"/>
-      <x:c r="K221" s="62"/>
+      <x:c r="K221" s="65"/>
+      <x:c r="L221" s="78"/>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="61"/>
@@ -3486,7 +3760,8 @@
       <x:c r="H222" s="62"/>
       <x:c r="I222" s="62"/>
       <x:c r="J222" s="64"/>
-      <x:c r="K222" s="62"/>
+      <x:c r="K222" s="65"/>
+      <x:c r="L222" s="78"/>
     </x:row>
     <x:row r="223">
       <x:c r="A223" s="61"/>
@@ -3499,7 +3774,8 @@
       <x:c r="H223" s="62"/>
       <x:c r="I223" s="62"/>
       <x:c r="J223" s="64"/>
-      <x:c r="K223" s="62"/>
+      <x:c r="K223" s="65"/>
+      <x:c r="L223" s="78"/>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="61"/>
@@ -3512,7 +3788,8 @@
       <x:c r="H224" s="62"/>
       <x:c r="I224" s="62"/>
       <x:c r="J224" s="64"/>
-      <x:c r="K224" s="62"/>
+      <x:c r="K224" s="65"/>
+      <x:c r="L224" s="78"/>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="61"/>
@@ -3525,7 +3802,8 @@
       <x:c r="H225" s="62"/>
       <x:c r="I225" s="62"/>
       <x:c r="J225" s="64"/>
-      <x:c r="K225" s="62"/>
+      <x:c r="K225" s="65"/>
+      <x:c r="L225" s="78"/>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="61"/>
@@ -3538,7 +3816,8 @@
       <x:c r="H226" s="62"/>
       <x:c r="I226" s="62"/>
       <x:c r="J226" s="64"/>
-      <x:c r="K226" s="62"/>
+      <x:c r="K226" s="65"/>
+      <x:c r="L226" s="78"/>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="61"/>
@@ -3551,7 +3830,8 @@
       <x:c r="H227" s="62"/>
       <x:c r="I227" s="62"/>
       <x:c r="J227" s="64"/>
-      <x:c r="K227" s="62"/>
+      <x:c r="K227" s="65"/>
+      <x:c r="L227" s="78"/>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="61"/>
@@ -3564,7 +3844,8 @@
       <x:c r="H228" s="62"/>
       <x:c r="I228" s="62"/>
       <x:c r="J228" s="64"/>
-      <x:c r="K228" s="62"/>
+      <x:c r="K228" s="65"/>
+      <x:c r="L228" s="78"/>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="61"/>
@@ -3577,7 +3858,8 @@
       <x:c r="H229" s="62"/>
       <x:c r="I229" s="62"/>
       <x:c r="J229" s="64"/>
-      <x:c r="K229" s="62"/>
+      <x:c r="K229" s="65"/>
+      <x:c r="L229" s="78"/>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="61"/>
@@ -3590,7 +3872,8 @@
       <x:c r="H230" s="62"/>
       <x:c r="I230" s="62"/>
       <x:c r="J230" s="64"/>
-      <x:c r="K230" s="62"/>
+      <x:c r="K230" s="65"/>
+      <x:c r="L230" s="78"/>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="61"/>
@@ -3603,7 +3886,8 @@
       <x:c r="H231" s="62"/>
       <x:c r="I231" s="62"/>
       <x:c r="J231" s="64"/>
-      <x:c r="K231" s="62"/>
+      <x:c r="K231" s="65"/>
+      <x:c r="L231" s="78"/>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="61"/>
@@ -3616,7 +3900,8 @@
       <x:c r="H232" s="62"/>
       <x:c r="I232" s="62"/>
       <x:c r="J232" s="64"/>
-      <x:c r="K232" s="62"/>
+      <x:c r="K232" s="65"/>
+      <x:c r="L232" s="78"/>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="61"/>
@@ -3629,7 +3914,8 @@
       <x:c r="H233" s="62"/>
       <x:c r="I233" s="62"/>
       <x:c r="J233" s="64"/>
-      <x:c r="K233" s="62"/>
+      <x:c r="K233" s="65"/>
+      <x:c r="L233" s="78"/>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="61"/>
@@ -3642,7 +3928,8 @@
       <x:c r="H234" s="62"/>
       <x:c r="I234" s="62"/>
       <x:c r="J234" s="64"/>
-      <x:c r="K234" s="62"/>
+      <x:c r="K234" s="65"/>
+      <x:c r="L234" s="78"/>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="61"/>
@@ -3655,7 +3942,8 @@
       <x:c r="H235" s="62"/>
       <x:c r="I235" s="62"/>
       <x:c r="J235" s="64"/>
-      <x:c r="K235" s="62"/>
+      <x:c r="K235" s="65"/>
+      <x:c r="L235" s="78"/>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="61"/>
@@ -3668,7 +3956,8 @@
       <x:c r="H236" s="62"/>
       <x:c r="I236" s="62"/>
       <x:c r="J236" s="64"/>
-      <x:c r="K236" s="62"/>
+      <x:c r="K236" s="65"/>
+      <x:c r="L236" s="78"/>
     </x:row>
     <x:row r="237">
       <x:c r="A237" s="61"/>
@@ -3681,7 +3970,8 @@
       <x:c r="H237" s="62"/>
       <x:c r="I237" s="62"/>
       <x:c r="J237" s="64"/>
-      <x:c r="K237" s="62"/>
+      <x:c r="K237" s="65"/>
+      <x:c r="L237" s="78"/>
     </x:row>
     <x:row r="238">
       <x:c r="A238" s="61"/>
@@ -3694,7 +3984,8 @@
       <x:c r="H238" s="62"/>
       <x:c r="I238" s="62"/>
       <x:c r="J238" s="64"/>
-      <x:c r="K238" s="62"/>
+      <x:c r="K238" s="65"/>
+      <x:c r="L238" s="78"/>
     </x:row>
     <x:row r="239">
       <x:c r="A239" s="61"/>
@@ -3707,7 +3998,8 @@
       <x:c r="H239" s="62"/>
       <x:c r="I239" s="62"/>
       <x:c r="J239" s="64"/>
-      <x:c r="K239" s="62"/>
+      <x:c r="K239" s="65"/>
+      <x:c r="L239" s="78"/>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="61"/>
@@ -3720,7 +4012,8 @@
       <x:c r="H240" s="62"/>
       <x:c r="I240" s="62"/>
       <x:c r="J240" s="64"/>
-      <x:c r="K240" s="62"/>
+      <x:c r="K240" s="65"/>
+      <x:c r="L240" s="78"/>
     </x:row>
     <x:row r="241">
       <x:c r="A241" s="61"/>
@@ -3733,7 +4026,8 @@
       <x:c r="H241" s="62"/>
       <x:c r="I241" s="62"/>
       <x:c r="J241" s="64"/>
-      <x:c r="K241" s="62"/>
+      <x:c r="K241" s="65"/>
+      <x:c r="L241" s="78"/>
     </x:row>
     <x:row r="242">
       <x:c r="A242" s="61"/>
@@ -3746,7 +4040,8 @@
       <x:c r="H242" s="62"/>
       <x:c r="I242" s="62"/>
       <x:c r="J242" s="64"/>
-      <x:c r="K242" s="62"/>
+      <x:c r="K242" s="65"/>
+      <x:c r="L242" s="78"/>
     </x:row>
     <x:row r="243">
       <x:c r="A243" s="61"/>
@@ -3759,7 +4054,8 @@
       <x:c r="H243" s="62"/>
       <x:c r="I243" s="62"/>
       <x:c r="J243" s="64"/>
-      <x:c r="K243" s="62"/>
+      <x:c r="K243" s="65"/>
+      <x:c r="L243" s="78"/>
     </x:row>
     <x:row r="244">
       <x:c r="A244" s="61"/>
@@ -3772,7 +4068,8 @@
       <x:c r="H244" s="62"/>
       <x:c r="I244" s="62"/>
       <x:c r="J244" s="64"/>
-      <x:c r="K244" s="62"/>
+      <x:c r="K244" s="65"/>
+      <x:c r="L244" s="78"/>
     </x:row>
     <x:row r="245">
       <x:c r="A245" s="61"/>
@@ -3785,7 +4082,8 @@
       <x:c r="H245" s="62"/>
       <x:c r="I245" s="62"/>
       <x:c r="J245" s="64"/>
-      <x:c r="K245" s="62"/>
+      <x:c r="K245" s="65"/>
+      <x:c r="L245" s="78"/>
     </x:row>
     <x:row r="246">
       <x:c r="A246" s="61"/>
@@ -3798,7 +4096,8 @@
       <x:c r="H246" s="62"/>
       <x:c r="I246" s="62"/>
       <x:c r="J246" s="64"/>
-      <x:c r="K246" s="62"/>
+      <x:c r="K246" s="65"/>
+      <x:c r="L246" s="78"/>
     </x:row>
     <x:row r="247">
       <x:c r="A247" s="61"/>
@@ -3811,7 +4110,8 @@
       <x:c r="H247" s="62"/>
       <x:c r="I247" s="62"/>
       <x:c r="J247" s="64"/>
-      <x:c r="K247" s="62"/>
+      <x:c r="K247" s="65"/>
+      <x:c r="L247" s="78"/>
     </x:row>
     <x:row r="248">
       <x:c r="A248" s="61"/>
@@ -3824,7 +4124,8 @@
       <x:c r="H248" s="62"/>
       <x:c r="I248" s="62"/>
       <x:c r="J248" s="64"/>
-      <x:c r="K248" s="62"/>
+      <x:c r="K248" s="65"/>
+      <x:c r="L248" s="78"/>
     </x:row>
     <x:row r="249">
       <x:c r="A249" s="61"/>
@@ -3837,7 +4138,8 @@
       <x:c r="H249" s="62"/>
       <x:c r="I249" s="62"/>
       <x:c r="J249" s="64"/>
-      <x:c r="K249" s="62"/>
+      <x:c r="K249" s="65"/>
+      <x:c r="L249" s="78"/>
     </x:row>
     <x:row r="250">
       <x:c r="A250" s="61"/>
@@ -3850,7 +4152,8 @@
       <x:c r="H250" s="62"/>
       <x:c r="I250" s="62"/>
       <x:c r="J250" s="64"/>
-      <x:c r="K250" s="62"/>
+      <x:c r="K250" s="65"/>
+      <x:c r="L250" s="78"/>
     </x:row>
     <x:row r="251">
       <x:c r="A251" s="61"/>
@@ -3863,7 +4166,8 @@
       <x:c r="H251" s="62"/>
       <x:c r="I251" s="62"/>
       <x:c r="J251" s="64"/>
-      <x:c r="K251" s="62"/>
+      <x:c r="K251" s="65"/>
+      <x:c r="L251" s="78"/>
     </x:row>
     <x:row r="252">
       <x:c r="A252" s="61"/>
@@ -3876,7 +4180,8 @@
       <x:c r="H252" s="62"/>
       <x:c r="I252" s="62"/>
       <x:c r="J252" s="64"/>
-      <x:c r="K252" s="62"/>
+      <x:c r="K252" s="65"/>
+      <x:c r="L252" s="78"/>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="61"/>
@@ -3889,7 +4194,8 @@
       <x:c r="H253" s="62"/>
       <x:c r="I253" s="62"/>
       <x:c r="J253" s="64"/>
-      <x:c r="K253" s="62"/>
+      <x:c r="K253" s="65"/>
+      <x:c r="L253" s="78"/>
     </x:row>
     <x:row r="254">
       <x:c r="A254" s="61"/>
@@ -3902,7 +4208,8 @@
       <x:c r="H254" s="62"/>
       <x:c r="I254" s="62"/>
       <x:c r="J254" s="64"/>
-      <x:c r="K254" s="62"/>
+      <x:c r="K254" s="65"/>
+      <x:c r="L254" s="78"/>
     </x:row>
     <x:row r="255">
       <x:c r="A255" s="61"/>
@@ -3915,7 +4222,8 @@
       <x:c r="H255" s="62"/>
       <x:c r="I255" s="62"/>
       <x:c r="J255" s="64"/>
-      <x:c r="K255" s="62"/>
+      <x:c r="K255" s="65"/>
+      <x:c r="L255" s="78"/>
     </x:row>
     <x:row r="256">
       <x:c r="A256" s="61"/>
@@ -3928,7 +4236,8 @@
       <x:c r="H256" s="62"/>
       <x:c r="I256" s="62"/>
       <x:c r="J256" s="64"/>
-      <x:c r="K256" s="62"/>
+      <x:c r="K256" s="65"/>
+      <x:c r="L256" s="78"/>
     </x:row>
     <x:row r="257">
       <x:c r="A257" s="61"/>
@@ -3941,7 +4250,8 @@
       <x:c r="H257" s="62"/>
       <x:c r="I257" s="62"/>
       <x:c r="J257" s="64"/>
-      <x:c r="K257" s="62"/>
+      <x:c r="K257" s="65"/>
+      <x:c r="L257" s="78"/>
     </x:row>
     <x:row r="258">
       <x:c r="A258" s="61"/>
@@ -3954,7 +4264,8 @@
       <x:c r="H258" s="62"/>
       <x:c r="I258" s="62"/>
       <x:c r="J258" s="64"/>
-      <x:c r="K258" s="62"/>
+      <x:c r="K258" s="65"/>
+      <x:c r="L258" s="78"/>
     </x:row>
     <x:row r="259">
       <x:c r="A259" s="61"/>
@@ -3967,7 +4278,8 @@
       <x:c r="H259" s="62"/>
       <x:c r="I259" s="62"/>
       <x:c r="J259" s="64"/>
-      <x:c r="K259" s="62"/>
+      <x:c r="K259" s="65"/>
+      <x:c r="L259" s="78"/>
     </x:row>
     <x:row r="260">
       <x:c r="A260" s="61"/>
@@ -3980,7 +4292,8 @@
       <x:c r="H260" s="62"/>
       <x:c r="I260" s="62"/>
       <x:c r="J260" s="64"/>
-      <x:c r="K260" s="62"/>
+      <x:c r="K260" s="65"/>
+      <x:c r="L260" s="78"/>
     </x:row>
     <x:row r="261">
       <x:c r="A261" s="61"/>
@@ -3993,7 +4306,8 @@
       <x:c r="H261" s="62"/>
       <x:c r="I261" s="62"/>
       <x:c r="J261" s="64"/>
-      <x:c r="K261" s="62"/>
+      <x:c r="K261" s="65"/>
+      <x:c r="L261" s="78"/>
     </x:row>
     <x:row r="262">
       <x:c r="A262" s="61"/>
@@ -4006,7 +4320,8 @@
       <x:c r="H262" s="62"/>
       <x:c r="I262" s="62"/>
       <x:c r="J262" s="64"/>
-      <x:c r="K262" s="62"/>
+      <x:c r="K262" s="65"/>
+      <x:c r="L262" s="78"/>
     </x:row>
     <x:row r="263">
       <x:c r="A263" s="61"/>
@@ -4019,7 +4334,8 @@
       <x:c r="H263" s="62"/>
       <x:c r="I263" s="62"/>
       <x:c r="J263" s="64"/>
-      <x:c r="K263" s="62"/>
+      <x:c r="K263" s="65"/>
+      <x:c r="L263" s="78"/>
     </x:row>
     <x:row r="264">
       <x:c r="A264" s="61"/>
@@ -4032,7 +4348,8 @@
       <x:c r="H264" s="62"/>
       <x:c r="I264" s="62"/>
       <x:c r="J264" s="64"/>
-      <x:c r="K264" s="62"/>
+      <x:c r="K264" s="65"/>
+      <x:c r="L264" s="78"/>
     </x:row>
     <x:row r="265">
       <x:c r="A265" s="61"/>
@@ -4045,7 +4362,8 @@
       <x:c r="H265" s="62"/>
       <x:c r="I265" s="62"/>
       <x:c r="J265" s="64"/>
-      <x:c r="K265" s="62"/>
+      <x:c r="K265" s="65"/>
+      <x:c r="L265" s="78"/>
     </x:row>
     <x:row r="266">
       <x:c r="A266" s="61"/>
@@ -4058,7 +4376,8 @@
       <x:c r="H266" s="62"/>
       <x:c r="I266" s="62"/>
       <x:c r="J266" s="64"/>
-      <x:c r="K266" s="62"/>
+      <x:c r="K266" s="65"/>
+      <x:c r="L266" s="78"/>
     </x:row>
     <x:row r="267">
       <x:c r="A267" s="61"/>
@@ -4071,7 +4390,8 @@
       <x:c r="H267" s="62"/>
       <x:c r="I267" s="62"/>
       <x:c r="J267" s="64"/>
-      <x:c r="K267" s="62"/>
+      <x:c r="K267" s="65"/>
+      <x:c r="L267" s="78"/>
     </x:row>
     <x:row r="268">
       <x:c r="A268" s="61"/>
@@ -4084,7 +4404,8 @@
       <x:c r="H268" s="62"/>
       <x:c r="I268" s="62"/>
       <x:c r="J268" s="64"/>
-      <x:c r="K268" s="62"/>
+      <x:c r="K268" s="65"/>
+      <x:c r="L268" s="78"/>
     </x:row>
     <x:row r="269">
       <x:c r="A269" s="61"/>
@@ -4097,7 +4418,8 @@
       <x:c r="H269" s="62"/>
       <x:c r="I269" s="62"/>
       <x:c r="J269" s="64"/>
-      <x:c r="K269" s="62"/>
+      <x:c r="K269" s="65"/>
+      <x:c r="L269" s="78"/>
     </x:row>
     <x:row r="270">
       <x:c r="A270" s="61"/>
@@ -4110,7 +4432,8 @@
       <x:c r="H270" s="62"/>
       <x:c r="I270" s="62"/>
       <x:c r="J270" s="64"/>
-      <x:c r="K270" s="62"/>
+      <x:c r="K270" s="65"/>
+      <x:c r="L270" s="78"/>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="61"/>
@@ -4123,7 +4446,8 @@
       <x:c r="H271" s="62"/>
       <x:c r="I271" s="62"/>
       <x:c r="J271" s="64"/>
-      <x:c r="K271" s="62"/>
+      <x:c r="K271" s="65"/>
+      <x:c r="L271" s="78"/>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="61"/>
@@ -4136,7 +4460,8 @@
       <x:c r="H272" s="62"/>
       <x:c r="I272" s="62"/>
       <x:c r="J272" s="64"/>
-      <x:c r="K272" s="62"/>
+      <x:c r="K272" s="65"/>
+      <x:c r="L272" s="78"/>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="61"/>
@@ -4149,7 +4474,8 @@
       <x:c r="H273" s="62"/>
       <x:c r="I273" s="62"/>
       <x:c r="J273" s="64"/>
-      <x:c r="K273" s="62"/>
+      <x:c r="K273" s="65"/>
+      <x:c r="L273" s="78"/>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="61"/>
@@ -4162,7 +4488,8 @@
       <x:c r="H274" s="62"/>
       <x:c r="I274" s="62"/>
       <x:c r="J274" s="64"/>
-      <x:c r="K274" s="62"/>
+      <x:c r="K274" s="65"/>
+      <x:c r="L274" s="78"/>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="61"/>
@@ -4175,7 +4502,8 @@
       <x:c r="H275" s="62"/>
       <x:c r="I275" s="62"/>
       <x:c r="J275" s="64"/>
-      <x:c r="K275" s="62"/>
+      <x:c r="K275" s="65"/>
+      <x:c r="L275" s="78"/>
     </x:row>
     <x:row r="276">
       <x:c r="A276" s="61"/>
@@ -4188,7 +4516,8 @@
       <x:c r="H276" s="62"/>
       <x:c r="I276" s="62"/>
       <x:c r="J276" s="64"/>
-      <x:c r="K276" s="62"/>
+      <x:c r="K276" s="65"/>
+      <x:c r="L276" s="78"/>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="61"/>
@@ -4201,7 +4530,8 @@
       <x:c r="H277" s="62"/>
       <x:c r="I277" s="62"/>
       <x:c r="J277" s="64"/>
-      <x:c r="K277" s="62"/>
+      <x:c r="K277" s="65"/>
+      <x:c r="L277" s="78"/>
     </x:row>
     <x:row r="278">
       <x:c r="A278" s="61"/>
@@ -4214,7 +4544,8 @@
       <x:c r="H278" s="62"/>
       <x:c r="I278" s="62"/>
       <x:c r="J278" s="64"/>
-      <x:c r="K278" s="62"/>
+      <x:c r="K278" s="65"/>
+      <x:c r="L278" s="78"/>
     </x:row>
     <x:row r="279">
       <x:c r="A279" s="61"/>
@@ -4227,7 +4558,8 @@
       <x:c r="H279" s="62"/>
       <x:c r="I279" s="62"/>
       <x:c r="J279" s="64"/>
-      <x:c r="K279" s="62"/>
+      <x:c r="K279" s="65"/>
+      <x:c r="L279" s="78"/>
     </x:row>
     <x:row r="280">
       <x:c r="A280" s="61"/>
@@ -4240,7 +4572,8 @@
       <x:c r="H280" s="62"/>
       <x:c r="I280" s="62"/>
       <x:c r="J280" s="64"/>
-      <x:c r="K280" s="62"/>
+      <x:c r="K280" s="65"/>
+      <x:c r="L280" s="78"/>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="61"/>
@@ -4253,7 +4586,8 @@
       <x:c r="H281" s="62"/>
       <x:c r="I281" s="62"/>
       <x:c r="J281" s="64"/>
-      <x:c r="K281" s="62"/>
+      <x:c r="K281" s="65"/>
+      <x:c r="L281" s="78"/>
     </x:row>
     <x:row r="282">
       <x:c r="A282" s="61"/>
@@ -4266,7 +4600,8 @@
       <x:c r="H282" s="62"/>
       <x:c r="I282" s="62"/>
       <x:c r="J282" s="64"/>
-      <x:c r="K282" s="62"/>
+      <x:c r="K282" s="65"/>
+      <x:c r="L282" s="78"/>
     </x:row>
     <x:row r="283">
       <x:c r="A283" s="61"/>
@@ -4279,7 +4614,8 @@
       <x:c r="H283" s="62"/>
       <x:c r="I283" s="62"/>
       <x:c r="J283" s="64"/>
-      <x:c r="K283" s="62"/>
+      <x:c r="K283" s="65"/>
+      <x:c r="L283" s="78"/>
     </x:row>
     <x:row r="284">
       <x:c r="A284" s="61"/>
@@ -4292,7 +4628,8 @@
       <x:c r="H284" s="62"/>
       <x:c r="I284" s="62"/>
       <x:c r="J284" s="64"/>
-      <x:c r="K284" s="62"/>
+      <x:c r="K284" s="65"/>
+      <x:c r="L284" s="78"/>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="61"/>
@@ -4305,7 +4642,8 @@
       <x:c r="H285" s="62"/>
       <x:c r="I285" s="62"/>
       <x:c r="J285" s="64"/>
-      <x:c r="K285" s="62"/>
+      <x:c r="K285" s="65"/>
+      <x:c r="L285" s="78"/>
     </x:row>
     <x:row r="286">
       <x:c r="A286" s="61"/>
@@ -4318,7 +4656,8 @@
       <x:c r="H286" s="62"/>
       <x:c r="I286" s="62"/>
       <x:c r="J286" s="64"/>
-      <x:c r="K286" s="62"/>
+      <x:c r="K286" s="65"/>
+      <x:c r="L286" s="78"/>
     </x:row>
     <x:row r="287">
       <x:c r="A287" s="61"/>
@@ -4331,7 +4670,8 @@
       <x:c r="H287" s="62"/>
       <x:c r="I287" s="62"/>
       <x:c r="J287" s="64"/>
-      <x:c r="K287" s="62"/>
+      <x:c r="K287" s="65"/>
+      <x:c r="L287" s="78"/>
     </x:row>
     <x:row r="288">
       <x:c r="A288" s="61"/>
@@ -4344,7 +4684,8 @@
       <x:c r="H288" s="62"/>
       <x:c r="I288" s="62"/>
       <x:c r="J288" s="64"/>
-      <x:c r="K288" s="62"/>
+      <x:c r="K288" s="65"/>
+      <x:c r="L288" s="78"/>
     </x:row>
     <x:row r="289">
       <x:c r="A289" s="61"/>
@@ -4357,7 +4698,8 @@
       <x:c r="H289" s="62"/>
       <x:c r="I289" s="62"/>
       <x:c r="J289" s="64"/>
-      <x:c r="K289" s="62"/>
+      <x:c r="K289" s="65"/>
+      <x:c r="L289" s="78"/>
     </x:row>
     <x:row r="290">
       <x:c r="A290" s="61"/>
@@ -4370,7 +4712,8 @@
       <x:c r="H290" s="62"/>
       <x:c r="I290" s="62"/>
       <x:c r="J290" s="64"/>
-      <x:c r="K290" s="62"/>
+      <x:c r="K290" s="65"/>
+      <x:c r="L290" s="78"/>
     </x:row>
     <x:row r="291">
       <x:c r="A291" s="61"/>
@@ -4383,7 +4726,8 @@
       <x:c r="H291" s="62"/>
       <x:c r="I291" s="62"/>
       <x:c r="J291" s="64"/>
-      <x:c r="K291" s="62"/>
+      <x:c r="K291" s="65"/>
+      <x:c r="L291" s="78"/>
     </x:row>
     <x:row r="292">
       <x:c r="A292" s="61"/>
@@ -4396,7 +4740,8 @@
       <x:c r="H292" s="62"/>
       <x:c r="I292" s="62"/>
       <x:c r="J292" s="64"/>
-      <x:c r="K292" s="62"/>
+      <x:c r="K292" s="65"/>
+      <x:c r="L292" s="78"/>
     </x:row>
     <x:row r="293">
       <x:c r="A293" s="61"/>
@@ -4409,7 +4754,8 @@
       <x:c r="H293" s="62"/>
       <x:c r="I293" s="62"/>
       <x:c r="J293" s="64"/>
-      <x:c r="K293" s="62"/>
+      <x:c r="K293" s="65"/>
+      <x:c r="L293" s="78"/>
     </x:row>
     <x:row r="294">
       <x:c r="A294" s="61"/>
@@ -4422,7 +4768,8 @@
       <x:c r="H294" s="62"/>
       <x:c r="I294" s="62"/>
       <x:c r="J294" s="64"/>
-      <x:c r="K294" s="62"/>
+      <x:c r="K294" s="65"/>
+      <x:c r="L294" s="78"/>
     </x:row>
     <x:row r="295">
       <x:c r="A295" s="61"/>
@@ -4435,7 +4782,8 @@
       <x:c r="H295" s="62"/>
       <x:c r="I295" s="62"/>
       <x:c r="J295" s="64"/>
-      <x:c r="K295" s="62"/>
+      <x:c r="K295" s="65"/>
+      <x:c r="L295" s="78"/>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="61"/>
@@ -4448,7 +4796,8 @@
       <x:c r="H296" s="62"/>
       <x:c r="I296" s="62"/>
       <x:c r="J296" s="64"/>
-      <x:c r="K296" s="62"/>
+      <x:c r="K296" s="65"/>
+      <x:c r="L296" s="78"/>
     </x:row>
     <x:row r="297">
       <x:c r="A297" s="61"/>
@@ -4461,7 +4810,8 @@
       <x:c r="H297" s="62"/>
       <x:c r="I297" s="62"/>
       <x:c r="J297" s="64"/>
-      <x:c r="K297" s="62"/>
+      <x:c r="K297" s="65"/>
+      <x:c r="L297" s="78"/>
     </x:row>
     <x:row r="298">
       <x:c r="A298" s="61"/>
@@ -4474,7 +4824,8 @@
       <x:c r="H298" s="62"/>
       <x:c r="I298" s="62"/>
       <x:c r="J298" s="64"/>
-      <x:c r="K298" s="62"/>
+      <x:c r="K298" s="65"/>
+      <x:c r="L298" s="78"/>
     </x:row>
     <x:row r="299">
       <x:c r="A299" s="61"/>
@@ -4487,7 +4838,8 @@
       <x:c r="H299" s="62"/>
       <x:c r="I299" s="62"/>
       <x:c r="J299" s="64"/>
-      <x:c r="K299" s="62"/>
+      <x:c r="K299" s="65"/>
+      <x:c r="L299" s="78"/>
     </x:row>
     <x:row r="300">
       <x:c r="A300" s="61"/>
@@ -4500,7 +4852,8 @@
       <x:c r="H300" s="62"/>
       <x:c r="I300" s="62"/>
       <x:c r="J300" s="64"/>
-      <x:c r="K300" s="62"/>
+      <x:c r="K300" s="65"/>
+      <x:c r="L300" s="78"/>
     </x:row>
     <x:row r="301">
       <x:c r="A301" s="61"/>
@@ -4513,7 +4866,8 @@
       <x:c r="H301" s="62"/>
       <x:c r="I301" s="62"/>
       <x:c r="J301" s="64"/>
-      <x:c r="K301" s="62"/>
+      <x:c r="K301" s="65"/>
+      <x:c r="L301" s="78"/>
     </x:row>
     <x:row r="302">
       <x:c r="A302" s="61"/>
@@ -4526,7 +4880,8 @@
       <x:c r="H302" s="62"/>
       <x:c r="I302" s="62"/>
       <x:c r="J302" s="64"/>
-      <x:c r="K302" s="62"/>
+      <x:c r="K302" s="65"/>
+      <x:c r="L302" s="78"/>
     </x:row>
     <x:row r="303">
       <x:c r="A303" s="61"/>
@@ -4539,7 +4894,8 @@
       <x:c r="H303" s="62"/>
       <x:c r="I303" s="62"/>
       <x:c r="J303" s="64"/>
-      <x:c r="K303" s="62"/>
+      <x:c r="K303" s="65"/>
+      <x:c r="L303" s="78"/>
     </x:row>
     <x:row r="304">
       <x:c r="A304" s="61"/>
@@ -4552,7 +4908,8 @@
       <x:c r="H304" s="62"/>
       <x:c r="I304" s="62"/>
       <x:c r="J304" s="64"/>
-      <x:c r="K304" s="62"/>
+      <x:c r="K304" s="65"/>
+      <x:c r="L304" s="78"/>
     </x:row>
     <x:row r="305">
       <x:c r="A305" s="61"/>
@@ -4565,7 +4922,8 @@
       <x:c r="H305" s="62"/>
       <x:c r="I305" s="62"/>
       <x:c r="J305" s="64"/>
-      <x:c r="K305" s="62"/>
+      <x:c r="K305" s="65"/>
+      <x:c r="L305" s="78"/>
     </x:row>
     <x:row r="306">
       <x:c r="A306" s="61"/>
@@ -4578,7 +4936,8 @@
       <x:c r="H306" s="62"/>
       <x:c r="I306" s="62"/>
       <x:c r="J306" s="64"/>
-      <x:c r="K306" s="62"/>
+      <x:c r="K306" s="65"/>
+      <x:c r="L306" s="78"/>
     </x:row>
     <x:row r="307">
       <x:c r="A307" s="61"/>
@@ -4591,7 +4950,8 @@
       <x:c r="H307" s="62"/>
       <x:c r="I307" s="62"/>
       <x:c r="J307" s="64"/>
-      <x:c r="K307" s="62"/>
+      <x:c r="K307" s="65"/>
+      <x:c r="L307" s="78"/>
     </x:row>
     <x:row r="308">
       <x:c r="A308" s="61"/>
@@ -4604,7 +4964,8 @@
       <x:c r="H308" s="62"/>
       <x:c r="I308" s="62"/>
       <x:c r="J308" s="64"/>
-      <x:c r="K308" s="62"/>
+      <x:c r="K308" s="65"/>
+      <x:c r="L308" s="78"/>
     </x:row>
     <x:row r="309">
       <x:c r="A309" s="61"/>
@@ -4617,7 +4978,8 @@
       <x:c r="H309" s="62"/>
       <x:c r="I309" s="62"/>
       <x:c r="J309" s="64"/>
-      <x:c r="K309" s="62"/>
+      <x:c r="K309" s="65"/>
+      <x:c r="L309" s="78"/>
     </x:row>
     <x:row r="310">
       <x:c r="A310" s="61"/>
@@ -4630,7 +4992,8 @@
       <x:c r="H310" s="62"/>
       <x:c r="I310" s="62"/>
       <x:c r="J310" s="64"/>
-      <x:c r="K310" s="62"/>
+      <x:c r="K310" s="65"/>
+      <x:c r="L310" s="78"/>
     </x:row>
     <x:row r="311">
       <x:c r="A311" s="61"/>
@@ -4643,7 +5006,8 @@
       <x:c r="H311" s="62"/>
       <x:c r="I311" s="62"/>
       <x:c r="J311" s="64"/>
-      <x:c r="K311" s="62"/>
+      <x:c r="K311" s="65"/>
+      <x:c r="L311" s="78"/>
     </x:row>
     <x:row r="312">
       <x:c r="A312" s="61"/>
@@ -4656,7 +5020,8 @@
       <x:c r="H312" s="62"/>
       <x:c r="I312" s="62"/>
       <x:c r="J312" s="64"/>
-      <x:c r="K312" s="62"/>
+      <x:c r="K312" s="65"/>
+      <x:c r="L312" s="78"/>
     </x:row>
     <x:row r="313">
       <x:c r="A313" s="61"/>
@@ -4669,7 +5034,8 @@
       <x:c r="H313" s="62"/>
       <x:c r="I313" s="62"/>
       <x:c r="J313" s="64"/>
-      <x:c r="K313" s="62"/>
+      <x:c r="K313" s="65"/>
+      <x:c r="L313" s="78"/>
     </x:row>
     <x:row r="314">
       <x:c r="A314" s="61"/>
@@ -4682,7 +5048,8 @@
       <x:c r="H314" s="62"/>
       <x:c r="I314" s="62"/>
       <x:c r="J314" s="64"/>
-      <x:c r="K314" s="62"/>
+      <x:c r="K314" s="65"/>
+      <x:c r="L314" s="78"/>
     </x:row>
     <x:row r="315">
       <x:c r="A315" s="61"/>
@@ -4695,7 +5062,8 @@
       <x:c r="H315" s="62"/>
       <x:c r="I315" s="62"/>
       <x:c r="J315" s="64"/>
-      <x:c r="K315" s="62"/>
+      <x:c r="K315" s="65"/>
+      <x:c r="L315" s="78"/>
     </x:row>
     <x:row r="316">
       <x:c r="A316" s="61"/>
@@ -4708,7 +5076,8 @@
       <x:c r="H316" s="62"/>
       <x:c r="I316" s="62"/>
       <x:c r="J316" s="64"/>
-      <x:c r="K316" s="62"/>
+      <x:c r="K316" s="65"/>
+      <x:c r="L316" s="78"/>
     </x:row>
     <x:row r="317">
       <x:c r="A317" s="61"/>
@@ -4721,7 +5090,8 @@
       <x:c r="H317" s="62"/>
       <x:c r="I317" s="62"/>
       <x:c r="J317" s="64"/>
-      <x:c r="K317" s="62"/>
+      <x:c r="K317" s="65"/>
+      <x:c r="L317" s="78"/>
     </x:row>
     <x:row r="318">
       <x:c r="A318" s="61"/>
@@ -4734,7 +5104,8 @@
       <x:c r="H318" s="62"/>
       <x:c r="I318" s="62"/>
       <x:c r="J318" s="64"/>
-      <x:c r="K318" s="62"/>
+      <x:c r="K318" s="65"/>
+      <x:c r="L318" s="78"/>
     </x:row>
     <x:row r="319">
       <x:c r="A319" s="61"/>
@@ -4747,7 +5118,8 @@
       <x:c r="H319" s="62"/>
       <x:c r="I319" s="62"/>
       <x:c r="J319" s="64"/>
-      <x:c r="K319" s="62"/>
+      <x:c r="K319" s="65"/>
+      <x:c r="L319" s="78"/>
     </x:row>
     <x:row r="320">
       <x:c r="A320" s="61"/>
@@ -4760,7 +5132,8 @@
       <x:c r="H320" s="62"/>
       <x:c r="I320" s="62"/>
       <x:c r="J320" s="64"/>
-      <x:c r="K320" s="62"/>
+      <x:c r="K320" s="65"/>
+      <x:c r="L320" s="78"/>
     </x:row>
     <x:row r="321">
       <x:c r="A321" s="61"/>
@@ -4773,7 +5146,8 @@
       <x:c r="H321" s="62"/>
       <x:c r="I321" s="62"/>
       <x:c r="J321" s="64"/>
-      <x:c r="K321" s="62"/>
+      <x:c r="K321" s="65"/>
+      <x:c r="L321" s="78"/>
     </x:row>
     <x:row r="322">
       <x:c r="A322" s="61"/>
@@ -4786,7 +5160,8 @@
       <x:c r="H322" s="62"/>
       <x:c r="I322" s="62"/>
       <x:c r="J322" s="64"/>
-      <x:c r="K322" s="62"/>
+      <x:c r="K322" s="65"/>
+      <x:c r="L322" s="78"/>
     </x:row>
     <x:row r="323">
       <x:c r="A323" s="61"/>
@@ -4799,7 +5174,8 @@
       <x:c r="H323" s="62"/>
       <x:c r="I323" s="62"/>
       <x:c r="J323" s="64"/>
-      <x:c r="K323" s="62"/>
+      <x:c r="K323" s="65"/>
+      <x:c r="L323" s="78"/>
     </x:row>
     <x:row r="324">
       <x:c r="A324" s="61"/>
@@ -4812,7 +5188,8 @@
       <x:c r="H324" s="62"/>
       <x:c r="I324" s="62"/>
       <x:c r="J324" s="64"/>
-      <x:c r="K324" s="62"/>
+      <x:c r="K324" s="65"/>
+      <x:c r="L324" s="78"/>
     </x:row>
     <x:row r="325">
       <x:c r="A325" s="61"/>
@@ -4825,7 +5202,8 @@
       <x:c r="H325" s="62"/>
       <x:c r="I325" s="62"/>
       <x:c r="J325" s="64"/>
-      <x:c r="K325" s="62"/>
+      <x:c r="K325" s="65"/>
+      <x:c r="L325" s="78"/>
     </x:row>
     <x:row r="326">
       <x:c r="A326" s="61"/>
@@ -4838,7 +5216,8 @@
       <x:c r="H326" s="62"/>
       <x:c r="I326" s="62"/>
       <x:c r="J326" s="64"/>
-      <x:c r="K326" s="62"/>
+      <x:c r="K326" s="65"/>
+      <x:c r="L326" s="78"/>
     </x:row>
     <x:row r="327">
       <x:c r="A327" s="61"/>
@@ -4851,7 +5230,8 @@
       <x:c r="H327" s="62"/>
       <x:c r="I327" s="62"/>
       <x:c r="J327" s="64"/>
-      <x:c r="K327" s="62"/>
+      <x:c r="K327" s="65"/>
+      <x:c r="L327" s="78"/>
     </x:row>
     <x:row r="328">
       <x:c r="A328" s="61"/>
@@ -4864,7 +5244,8 @@
       <x:c r="H328" s="62"/>
       <x:c r="I328" s="62"/>
       <x:c r="J328" s="64"/>
-      <x:c r="K328" s="62"/>
+      <x:c r="K328" s="65"/>
+      <x:c r="L328" s="78"/>
     </x:row>
     <x:row r="329">
       <x:c r="A329" s="61"/>
@@ -4877,7 +5258,8 @@
       <x:c r="H329" s="62"/>
       <x:c r="I329" s="62"/>
       <x:c r="J329" s="64"/>
-      <x:c r="K329" s="62"/>
+      <x:c r="K329" s="65"/>
+      <x:c r="L329" s="78"/>
     </x:row>
     <x:row r="330">
       <x:c r="A330" s="61"/>
@@ -4890,7 +5272,8 @@
       <x:c r="H330" s="62"/>
       <x:c r="I330" s="62"/>
       <x:c r="J330" s="64"/>
-      <x:c r="K330" s="62"/>
+      <x:c r="K330" s="65"/>
+      <x:c r="L330" s="78"/>
     </x:row>
     <x:row r="331">
       <x:c r="A331" s="61"/>
@@ -4903,7 +5286,8 @@
       <x:c r="H331" s="62"/>
       <x:c r="I331" s="62"/>
       <x:c r="J331" s="64"/>
-      <x:c r="K331" s="62"/>
+      <x:c r="K331" s="65"/>
+      <x:c r="L331" s="78"/>
     </x:row>
     <x:row r="332">
       <x:c r="A332" s="61"/>
@@ -4916,7 +5300,8 @@
       <x:c r="H332" s="62"/>
       <x:c r="I332" s="62"/>
       <x:c r="J332" s="64"/>
-      <x:c r="K332" s="62"/>
+      <x:c r="K332" s="65"/>
+      <x:c r="L332" s="78"/>
     </x:row>
     <x:row r="333">
       <x:c r="A333" s="61"/>
@@ -4929,7 +5314,8 @@
       <x:c r="H333" s="62"/>
       <x:c r="I333" s="62"/>
       <x:c r="J333" s="64"/>
-      <x:c r="K333" s="62"/>
+      <x:c r="K333" s="65"/>
+      <x:c r="L333" s="78"/>
     </x:row>
     <x:row r="334">
       <x:c r="A334" s="61"/>
@@ -4942,7 +5328,8 @@
       <x:c r="H334" s="62"/>
       <x:c r="I334" s="62"/>
       <x:c r="J334" s="64"/>
-      <x:c r="K334" s="62"/>
+      <x:c r="K334" s="65"/>
+      <x:c r="L334" s="78"/>
     </x:row>
     <x:row r="335">
       <x:c r="A335" s="61"/>
@@ -4955,7 +5342,8 @@
       <x:c r="H335" s="62"/>
       <x:c r="I335" s="62"/>
       <x:c r="J335" s="64"/>
-      <x:c r="K335" s="62"/>
+      <x:c r="K335" s="65"/>
+      <x:c r="L335" s="78"/>
     </x:row>
     <x:row r="336">
       <x:c r="A336" s="61"/>
@@ -4968,7 +5356,8 @@
       <x:c r="H336" s="62"/>
       <x:c r="I336" s="62"/>
       <x:c r="J336" s="64"/>
-      <x:c r="K336" s="62"/>
+      <x:c r="K336" s="65"/>
+      <x:c r="L336" s="78"/>
     </x:row>
     <x:row r="337">
       <x:c r="A337" s="61"/>
@@ -4981,7 +5370,8 @@
       <x:c r="H337" s="62"/>
       <x:c r="I337" s="62"/>
       <x:c r="J337" s="64"/>
-      <x:c r="K337" s="62"/>
+      <x:c r="K337" s="65"/>
+      <x:c r="L337" s="78"/>
     </x:row>
     <x:row r="338">
       <x:c r="A338" s="61"/>
@@ -4994,7 +5384,8 @@
       <x:c r="H338" s="62"/>
       <x:c r="I338" s="62"/>
       <x:c r="J338" s="64"/>
-      <x:c r="K338" s="62"/>
+      <x:c r="K338" s="65"/>
+      <x:c r="L338" s="78"/>
     </x:row>
     <x:row r="339">
       <x:c r="A339" s="61"/>
@@ -5007,7 +5398,8 @@
       <x:c r="H339" s="62"/>
       <x:c r="I339" s="62"/>
       <x:c r="J339" s="64"/>
-      <x:c r="K339" s="62"/>
+      <x:c r="K339" s="65"/>
+      <x:c r="L339" s="78"/>
     </x:row>
     <x:row r="340">
       <x:c r="A340" s="61"/>
@@ -5020,7 +5412,8 @@
       <x:c r="H340" s="62"/>
       <x:c r="I340" s="62"/>
       <x:c r="J340" s="64"/>
-      <x:c r="K340" s="62"/>
+      <x:c r="K340" s="65"/>
+      <x:c r="L340" s="78"/>
     </x:row>
     <x:row r="341">
       <x:c r="A341" s="61"/>
@@ -5033,7 +5426,8 @@
       <x:c r="H341" s="62"/>
       <x:c r="I341" s="62"/>
       <x:c r="J341" s="64"/>
-      <x:c r="K341" s="62"/>
+      <x:c r="K341" s="65"/>
+      <x:c r="L341" s="78"/>
     </x:row>
     <x:row r="342">
       <x:c r="A342" s="61"/>
@@ -5046,7 +5440,8 @@
       <x:c r="H342" s="62"/>
       <x:c r="I342" s="62"/>
       <x:c r="J342" s="64"/>
-      <x:c r="K342" s="62"/>
+      <x:c r="K342" s="65"/>
+      <x:c r="L342" s="78"/>
     </x:row>
     <x:row r="343">
       <x:c r="A343" s="61"/>
@@ -5059,7 +5454,8 @@
       <x:c r="H343" s="62"/>
       <x:c r="I343" s="62"/>
       <x:c r="J343" s="64"/>
-      <x:c r="K343" s="62"/>
+      <x:c r="K343" s="65"/>
+      <x:c r="L343" s="78"/>
     </x:row>
     <x:row r="344">
       <x:c r="A344" s="61"/>
@@ -5072,7 +5468,8 @@
       <x:c r="H344" s="62"/>
       <x:c r="I344" s="62"/>
       <x:c r="J344" s="64"/>
-      <x:c r="K344" s="62"/>
+      <x:c r="K344" s="65"/>
+      <x:c r="L344" s="78"/>
     </x:row>
     <x:row r="345">
       <x:c r="A345" s="61"/>
@@ -5085,7 +5482,8 @@
       <x:c r="H345" s="62"/>
       <x:c r="I345" s="62"/>
       <x:c r="J345" s="64"/>
-      <x:c r="K345" s="62"/>
+      <x:c r="K345" s="65"/>
+      <x:c r="L345" s="78"/>
     </x:row>
     <x:row r="346">
       <x:c r="A346" s="61"/>
@@ -5098,7 +5496,8 @@
       <x:c r="H346" s="62"/>
       <x:c r="I346" s="62"/>
       <x:c r="J346" s="64"/>
-      <x:c r="K346" s="62"/>
+      <x:c r="K346" s="65"/>
+      <x:c r="L346" s="78"/>
     </x:row>
     <x:row r="347">
       <x:c r="A347" s="61"/>
@@ -5111,7 +5510,8 @@
       <x:c r="H347" s="62"/>
       <x:c r="I347" s="62"/>
       <x:c r="J347" s="64"/>
-      <x:c r="K347" s="62"/>
+      <x:c r="K347" s="65"/>
+      <x:c r="L347" s="78"/>
     </x:row>
     <x:row r="348">
       <x:c r="A348" s="61"/>
@@ -5124,7 +5524,8 @@
       <x:c r="H348" s="62"/>
       <x:c r="I348" s="62"/>
       <x:c r="J348" s="64"/>
-      <x:c r="K348" s="62"/>
+      <x:c r="K348" s="65"/>
+      <x:c r="L348" s="78"/>
     </x:row>
     <x:row r="349">
       <x:c r="A349" s="61"/>
@@ -5137,7 +5538,8 @@
       <x:c r="H349" s="62"/>
       <x:c r="I349" s="62"/>
       <x:c r="J349" s="64"/>
-      <x:c r="K349" s="62"/>
+      <x:c r="K349" s="65"/>
+      <x:c r="L349" s="78"/>
     </x:row>
     <x:row r="350">
       <x:c r="A350" s="61"/>
@@ -5150,7 +5552,8 @@
       <x:c r="H350" s="62"/>
       <x:c r="I350" s="62"/>
       <x:c r="J350" s="64"/>
-      <x:c r="K350" s="62"/>
+      <x:c r="K350" s="65"/>
+      <x:c r="L350" s="78"/>
     </x:row>
     <x:row r="351">
       <x:c r="A351" s="61"/>
@@ -5163,7 +5566,8 @@
       <x:c r="H351" s="62"/>
       <x:c r="I351" s="62"/>
       <x:c r="J351" s="64"/>
-      <x:c r="K351" s="62"/>
+      <x:c r="K351" s="65"/>
+      <x:c r="L351" s="78"/>
     </x:row>
     <x:row r="352">
       <x:c r="A352" s="61"/>
@@ -5176,7 +5580,8 @@
       <x:c r="H352" s="62"/>
       <x:c r="I352" s="62"/>
       <x:c r="J352" s="64"/>
-      <x:c r="K352" s="62"/>
+      <x:c r="K352" s="65"/>
+      <x:c r="L352" s="78"/>
     </x:row>
     <x:row r="353">
       <x:c r="A353" s="61"/>
@@ -5189,7 +5594,8 @@
       <x:c r="H353" s="62"/>
       <x:c r="I353" s="62"/>
       <x:c r="J353" s="64"/>
-      <x:c r="K353" s="62"/>
+      <x:c r="K353" s="65"/>
+      <x:c r="L353" s="78"/>
     </x:row>
     <x:row r="354">
       <x:c r="A354" s="61"/>
@@ -5202,7 +5608,8 @@
       <x:c r="H354" s="62"/>
       <x:c r="I354" s="62"/>
       <x:c r="J354" s="64"/>
-      <x:c r="K354" s="62"/>
+      <x:c r="K354" s="65"/>
+      <x:c r="L354" s="78"/>
     </x:row>
     <x:row r="355">
       <x:c r="A355" s="61"/>
@@ -5215,7 +5622,8 @@
       <x:c r="H355" s="62"/>
       <x:c r="I355" s="62"/>
       <x:c r="J355" s="64"/>
-      <x:c r="K355" s="62"/>
+      <x:c r="K355" s="65"/>
+      <x:c r="L355" s="78"/>
     </x:row>
     <x:row r="356">
       <x:c r="A356" s="61"/>
@@ -5228,7 +5636,8 @@
       <x:c r="H356" s="62"/>
       <x:c r="I356" s="62"/>
       <x:c r="J356" s="64"/>
-      <x:c r="K356" s="62"/>
+      <x:c r="K356" s="65"/>
+      <x:c r="L356" s="78"/>
     </x:row>
     <x:row r="357">
       <x:c r="A357" s="61"/>
@@ -5241,7 +5650,8 @@
       <x:c r="H357" s="62"/>
       <x:c r="I357" s="62"/>
       <x:c r="J357" s="64"/>
-      <x:c r="K357" s="62"/>
+      <x:c r="K357" s="65"/>
+      <x:c r="L357" s="78"/>
     </x:row>
     <x:row r="358">
       <x:c r="A358" s="61"/>
@@ -5254,7 +5664,8 @@
       <x:c r="H358" s="62"/>
       <x:c r="I358" s="62"/>
       <x:c r="J358" s="64"/>
-      <x:c r="K358" s="62"/>
+      <x:c r="K358" s="65"/>
+      <x:c r="L358" s="78"/>
     </x:row>
     <x:row r="359">
       <x:c r="A359" s="61"/>
@@ -5267,7 +5678,8 @@
       <x:c r="H359" s="62"/>
       <x:c r="I359" s="62"/>
       <x:c r="J359" s="64"/>
-      <x:c r="K359" s="62"/>
+      <x:c r="K359" s="65"/>
+      <x:c r="L359" s="78"/>
     </x:row>
     <x:row r="360">
       <x:c r="A360" s="61"/>
@@ -5280,7 +5692,8 @@
       <x:c r="H360" s="62"/>
       <x:c r="I360" s="62"/>
       <x:c r="J360" s="64"/>
-      <x:c r="K360" s="62"/>
+      <x:c r="K360" s="65"/>
+      <x:c r="L360" s="78"/>
     </x:row>
     <x:row r="361">
       <x:c r="A361" s="61"/>
@@ -5293,7 +5706,8 @@
       <x:c r="H361" s="62"/>
       <x:c r="I361" s="62"/>
       <x:c r="J361" s="64"/>
-      <x:c r="K361" s="62"/>
+      <x:c r="K361" s="65"/>
+      <x:c r="L361" s="78"/>
     </x:row>
     <x:row r="362">
       <x:c r="A362" s="61"/>
@@ -5306,7 +5720,8 @@
       <x:c r="H362" s="62"/>
       <x:c r="I362" s="62"/>
       <x:c r="J362" s="64"/>
-      <x:c r="K362" s="62"/>
+      <x:c r="K362" s="65"/>
+      <x:c r="L362" s="78"/>
     </x:row>
     <x:row r="363">
       <x:c r="A363" s="61"/>
@@ -5319,7 +5734,8 @@
       <x:c r="H363" s="62"/>
       <x:c r="I363" s="62"/>
       <x:c r="J363" s="64"/>
-      <x:c r="K363" s="62"/>
+      <x:c r="K363" s="65"/>
+      <x:c r="L363" s="78"/>
     </x:row>
     <x:row r="364">
       <x:c r="A364" s="61"/>
@@ -5332,7 +5748,8 @@
       <x:c r="H364" s="62"/>
       <x:c r="I364" s="62"/>
       <x:c r="J364" s="64"/>
-      <x:c r="K364" s="62"/>
+      <x:c r="K364" s="65"/>
+      <x:c r="L364" s="78"/>
     </x:row>
     <x:row r="365">
       <x:c r="A365" s="61"/>
@@ -5345,7 +5762,8 @@
       <x:c r="H365" s="62"/>
       <x:c r="I365" s="62"/>
       <x:c r="J365" s="64"/>
-      <x:c r="K365" s="62"/>
+      <x:c r="K365" s="65"/>
+      <x:c r="L365" s="78"/>
     </x:row>
     <x:row r="366">
       <x:c r="A366" s="61"/>
@@ -5358,7 +5776,8 @@
       <x:c r="H366" s="62"/>
       <x:c r="I366" s="62"/>
       <x:c r="J366" s="64"/>
-      <x:c r="K366" s="62"/>
+      <x:c r="K366" s="65"/>
+      <x:c r="L366" s="78"/>
     </x:row>
     <x:row r="367">
       <x:c r="A367" s="61"/>
@@ -5371,7 +5790,8 @@
       <x:c r="H367" s="62"/>
       <x:c r="I367" s="62"/>
       <x:c r="J367" s="64"/>
-      <x:c r="K367" s="62"/>
+      <x:c r="K367" s="65"/>
+      <x:c r="L367" s="78"/>
     </x:row>
     <x:row r="368">
       <x:c r="A368" s="61"/>
@@ -5384,7 +5804,8 @@
       <x:c r="H368" s="62"/>
       <x:c r="I368" s="62"/>
       <x:c r="J368" s="64"/>
-      <x:c r="K368" s="62"/>
+      <x:c r="K368" s="65"/>
+      <x:c r="L368" s="78"/>
     </x:row>
     <x:row r="369">
       <x:c r="A369" s="61"/>
@@ -5397,7 +5818,8 @@
       <x:c r="H369" s="62"/>
       <x:c r="I369" s="62"/>
       <x:c r="J369" s="64"/>
-      <x:c r="K369" s="62"/>
+      <x:c r="K369" s="65"/>
+      <x:c r="L369" s="78"/>
     </x:row>
     <x:row r="370">
       <x:c r="A370" s="61"/>
@@ -5410,7 +5832,8 @@
       <x:c r="H370" s="62"/>
       <x:c r="I370" s="62"/>
       <x:c r="J370" s="64"/>
-      <x:c r="K370" s="62"/>
+      <x:c r="K370" s="65"/>
+      <x:c r="L370" s="78"/>
     </x:row>
     <x:row r="371">
       <x:c r="A371" s="61"/>
@@ -5423,7 +5846,8 @@
       <x:c r="H371" s="62"/>
       <x:c r="I371" s="62"/>
       <x:c r="J371" s="64"/>
-      <x:c r="K371" s="62"/>
+      <x:c r="K371" s="65"/>
+      <x:c r="L371" s="78"/>
     </x:row>
     <x:row r="372">
       <x:c r="A372" s="61"/>
@@ -5436,7 +5860,8 @@
       <x:c r="H372" s="62"/>
       <x:c r="I372" s="62"/>
       <x:c r="J372" s="64"/>
-      <x:c r="K372" s="62"/>
+      <x:c r="K372" s="65"/>
+      <x:c r="L372" s="78"/>
     </x:row>
     <x:row r="373">
       <x:c r="A373" s="61"/>
@@ -5449,7 +5874,8 @@
       <x:c r="H373" s="62"/>
       <x:c r="I373" s="62"/>
       <x:c r="J373" s="64"/>
-      <x:c r="K373" s="62"/>
+      <x:c r="K373" s="65"/>
+      <x:c r="L373" s="78"/>
     </x:row>
     <x:row r="374">
       <x:c r="A374" s="61"/>
@@ -5462,7 +5888,8 @@
       <x:c r="H374" s="62"/>
       <x:c r="I374" s="62"/>
       <x:c r="J374" s="64"/>
-      <x:c r="K374" s="62"/>
+      <x:c r="K374" s="65"/>
+      <x:c r="L374" s="78"/>
     </x:row>
     <x:row r="375">
       <x:c r="A375" s="61"/>
@@ -5475,7 +5902,8 @@
       <x:c r="H375" s="62"/>
       <x:c r="I375" s="62"/>
       <x:c r="J375" s="64"/>
-      <x:c r="K375" s="62"/>
+      <x:c r="K375" s="65"/>
+      <x:c r="L375" s="78"/>
     </x:row>
     <x:row r="376">
       <x:c r="A376" s="61"/>
@@ -5488,7 +5916,8 @@
       <x:c r="H376" s="62"/>
       <x:c r="I376" s="62"/>
       <x:c r="J376" s="64"/>
-      <x:c r="K376" s="62"/>
+      <x:c r="K376" s="65"/>
+      <x:c r="L376" s="78"/>
     </x:row>
     <x:row r="377">
       <x:c r="A377" s="61"/>
@@ -5501,7 +5930,8 @@
       <x:c r="H377" s="62"/>
       <x:c r="I377" s="62"/>
       <x:c r="J377" s="64"/>
-      <x:c r="K377" s="62"/>
+      <x:c r="K377" s="65"/>
+      <x:c r="L377" s="78"/>
     </x:row>
     <x:row r="378">
       <x:c r="A378" s="61"/>
@@ -5514,7 +5944,8 @@
       <x:c r="H378" s="62"/>
       <x:c r="I378" s="62"/>
       <x:c r="J378" s="64"/>
-      <x:c r="K378" s="62"/>
+      <x:c r="K378" s="65"/>
+      <x:c r="L378" s="78"/>
     </x:row>
     <x:row r="379">
       <x:c r="A379" s="61"/>
@@ -5527,7 +5958,8 @@
       <x:c r="H379" s="62"/>
       <x:c r="I379" s="62"/>
       <x:c r="J379" s="64"/>
-      <x:c r="K379" s="62"/>
+      <x:c r="K379" s="65"/>
+      <x:c r="L379" s="78"/>
     </x:row>
     <x:row r="380">
       <x:c r="A380" s="61"/>
@@ -5540,7 +5972,8 @@
       <x:c r="H380" s="62"/>
       <x:c r="I380" s="62"/>
       <x:c r="J380" s="64"/>
-      <x:c r="K380" s="62"/>
+      <x:c r="K380" s="65"/>
+      <x:c r="L380" s="78"/>
     </x:row>
     <x:row r="381">
       <x:c r="A381" s="61"/>
@@ -5553,7 +5986,8 @@
       <x:c r="H381" s="62"/>
       <x:c r="I381" s="62"/>
       <x:c r="J381" s="64"/>
-      <x:c r="K381" s="62"/>
+      <x:c r="K381" s="65"/>
+      <x:c r="L381" s="78"/>
     </x:row>
     <x:row r="382">
       <x:c r="A382" s="61"/>
@@ -5566,7 +6000,8 @@
       <x:c r="H382" s="62"/>
       <x:c r="I382" s="62"/>
       <x:c r="J382" s="64"/>
-      <x:c r="K382" s="62"/>
+      <x:c r="K382" s="65"/>
+      <x:c r="L382" s="78"/>
     </x:row>
     <x:row r="383">
       <x:c r="A383" s="61"/>
@@ -5579,7 +6014,8 @@
       <x:c r="H383" s="62"/>
       <x:c r="I383" s="62"/>
       <x:c r="J383" s="64"/>
-      <x:c r="K383" s="62"/>
+      <x:c r="K383" s="65"/>
+      <x:c r="L383" s="78"/>
     </x:row>
     <x:row r="384">
       <x:c r="A384" s="61"/>
@@ -5592,7 +6028,8 @@
       <x:c r="H384" s="62"/>
       <x:c r="I384" s="62"/>
       <x:c r="J384" s="64"/>
-      <x:c r="K384" s="62"/>
+      <x:c r="K384" s="65"/>
+      <x:c r="L384" s="78"/>
     </x:row>
     <x:row r="385">
       <x:c r="A385" s="61"/>
@@ -5605,7 +6042,8 @@
       <x:c r="H385" s="62"/>
       <x:c r="I385" s="62"/>
       <x:c r="J385" s="64"/>
-      <x:c r="K385" s="62"/>
+      <x:c r="K385" s="65"/>
+      <x:c r="L385" s="78"/>
     </x:row>
     <x:row r="386">
       <x:c r="A386" s="61"/>
@@ -5618,7 +6056,8 @@
       <x:c r="H386" s="62"/>
       <x:c r="I386" s="62"/>
       <x:c r="J386" s="64"/>
-      <x:c r="K386" s="62"/>
+      <x:c r="K386" s="65"/>
+      <x:c r="L386" s="78"/>
     </x:row>
     <x:row r="387">
       <x:c r="A387" s="61"/>
@@ -5631,7 +6070,8 @@
       <x:c r="H387" s="62"/>
       <x:c r="I387" s="62"/>
       <x:c r="J387" s="64"/>
-      <x:c r="K387" s="62"/>
+      <x:c r="K387" s="65"/>
+      <x:c r="L387" s="78"/>
     </x:row>
     <x:row r="388">
       <x:c r="A388" s="61"/>
@@ -5644,7 +6084,8 @@
       <x:c r="H388" s="62"/>
       <x:c r="I388" s="62"/>
       <x:c r="J388" s="64"/>
-      <x:c r="K388" s="62"/>
+      <x:c r="K388" s="65"/>
+      <x:c r="L388" s="78"/>
     </x:row>
     <x:row r="389">
       <x:c r="A389" s="61"/>
@@ -5657,7 +6098,8 @@
       <x:c r="H389" s="62"/>
       <x:c r="I389" s="62"/>
       <x:c r="J389" s="64"/>
-      <x:c r="K389" s="62"/>
+      <x:c r="K389" s="65"/>
+      <x:c r="L389" s="78"/>
     </x:row>
     <x:row r="390">
       <x:c r="A390" s="61"/>
@@ -5670,7 +6112,8 @@
       <x:c r="H390" s="62"/>
       <x:c r="I390" s="62"/>
       <x:c r="J390" s="64"/>
-      <x:c r="K390" s="62"/>
+      <x:c r="K390" s="65"/>
+      <x:c r="L390" s="78"/>
     </x:row>
     <x:row r="391">
       <x:c r="A391" s="61"/>
@@ -5683,7 +6126,8 @@
       <x:c r="H391" s="62"/>
       <x:c r="I391" s="62"/>
       <x:c r="J391" s="64"/>
-      <x:c r="K391" s="62"/>
+      <x:c r="K391" s="65"/>
+      <x:c r="L391" s="78"/>
     </x:row>
     <x:row r="392">
       <x:c r="A392" s="61"/>
@@ -5696,7 +6140,8 @@
       <x:c r="H392" s="62"/>
       <x:c r="I392" s="62"/>
       <x:c r="J392" s="64"/>
-      <x:c r="K392" s="62"/>
+      <x:c r="K392" s="65"/>
+      <x:c r="L392" s="78"/>
     </x:row>
     <x:row r="393">
       <x:c r="A393" s="61"/>
@@ -5709,7 +6154,8 @@
       <x:c r="H393" s="62"/>
       <x:c r="I393" s="62"/>
       <x:c r="J393" s="64"/>
-      <x:c r="K393" s="62"/>
+      <x:c r="K393" s="65"/>
+      <x:c r="L393" s="78"/>
     </x:row>
     <x:row r="394">
       <x:c r="A394" s="61"/>
@@ -5722,7 +6168,8 @@
       <x:c r="H394" s="62"/>
       <x:c r="I394" s="62"/>
       <x:c r="J394" s="64"/>
-      <x:c r="K394" s="62"/>
+      <x:c r="K394" s="65"/>
+      <x:c r="L394" s="78"/>
     </x:row>
     <x:row r="395">
       <x:c r="A395" s="61"/>
@@ -5735,7 +6182,8 @@
       <x:c r="H395" s="62"/>
       <x:c r="I395" s="62"/>
       <x:c r="J395" s="64"/>
-      <x:c r="K395" s="62"/>
+      <x:c r="K395" s="65"/>
+      <x:c r="L395" s="78"/>
     </x:row>
     <x:row r="396">
       <x:c r="A396" s="61"/>
@@ -5748,7 +6196,8 @@
       <x:c r="H396" s="62"/>
       <x:c r="I396" s="62"/>
       <x:c r="J396" s="64"/>
-      <x:c r="K396" s="62"/>
+      <x:c r="K396" s="65"/>
+      <x:c r="L396" s="78"/>
     </x:row>
     <x:row r="397">
       <x:c r="A397" s="61"/>
@@ -5761,7 +6210,8 @@
       <x:c r="H397" s="62"/>
       <x:c r="I397" s="62"/>
       <x:c r="J397" s="64"/>
-      <x:c r="K397" s="62"/>
+      <x:c r="K397" s="65"/>
+      <x:c r="L397" s="78"/>
     </x:row>
     <x:row r="398">
       <x:c r="A398" s="61"/>
@@ -5774,7 +6224,8 @@
       <x:c r="H398" s="62"/>
       <x:c r="I398" s="62"/>
       <x:c r="J398" s="64"/>
-      <x:c r="K398" s="62"/>
+      <x:c r="K398" s="65"/>
+      <x:c r="L398" s="78"/>
     </x:row>
     <x:row r="399">
       <x:c r="A399" s="61"/>
@@ -5787,7 +6238,8 @@
       <x:c r="H399" s="62"/>
       <x:c r="I399" s="62"/>
       <x:c r="J399" s="64"/>
-      <x:c r="K399" s="62"/>
+      <x:c r="K399" s="65"/>
+      <x:c r="L399" s="78"/>
     </x:row>
     <x:row r="400">
       <x:c r="A400" s="61"/>
@@ -5800,7 +6252,8 @@
       <x:c r="H400" s="62"/>
       <x:c r="I400" s="62"/>
       <x:c r="J400" s="64"/>
-      <x:c r="K400" s="62"/>
+      <x:c r="K400" s="65"/>
+      <x:c r="L400" s="78"/>
     </x:row>
     <x:row r="401">
       <x:c r="A401" s="61"/>
@@ -5813,7 +6266,8 @@
       <x:c r="H401" s="62"/>
       <x:c r="I401" s="62"/>
       <x:c r="J401" s="64"/>
-      <x:c r="K401" s="62"/>
+      <x:c r="K401" s="65"/>
+      <x:c r="L401" s="78"/>
     </x:row>
     <x:row r="402">
       <x:c r="A402" s="61"/>
@@ -5826,7 +6280,8 @@
       <x:c r="H402" s="62"/>
       <x:c r="I402" s="62"/>
       <x:c r="J402" s="64"/>
-      <x:c r="K402" s="62"/>
+      <x:c r="K402" s="65"/>
+      <x:c r="L402" s="78"/>
     </x:row>
     <x:row r="403">
       <x:c r="A403" s="61"/>
@@ -5839,7 +6294,8 @@
       <x:c r="H403" s="62"/>
       <x:c r="I403" s="62"/>
       <x:c r="J403" s="64"/>
-      <x:c r="K403" s="62"/>
+      <x:c r="K403" s="65"/>
+      <x:c r="L403" s="78"/>
     </x:row>
     <x:row r="404">
       <x:c r="A404" s="61"/>
@@ -5852,7 +6308,8 @@
       <x:c r="H404" s="62"/>
       <x:c r="I404" s="62"/>
       <x:c r="J404" s="64"/>
-      <x:c r="K404" s="62"/>
+      <x:c r="K404" s="65"/>
+      <x:c r="L404" s="78"/>
     </x:row>
     <x:row r="405">
       <x:c r="A405" s="61"/>
@@ -5865,7 +6322,8 @@
       <x:c r="H405" s="62"/>
       <x:c r="I405" s="62"/>
       <x:c r="J405" s="64"/>
-      <x:c r="K405" s="62"/>
+      <x:c r="K405" s="65"/>
+      <x:c r="L405" s="78"/>
     </x:row>
     <x:row r="406">
       <x:c r="A406" s="61"/>
@@ -5878,7 +6336,8 @@
       <x:c r="H406" s="62"/>
       <x:c r="I406" s="62"/>
       <x:c r="J406" s="64"/>
-      <x:c r="K406" s="62"/>
+      <x:c r="K406" s="65"/>
+      <x:c r="L406" s="78"/>
     </x:row>
     <x:row r="407">
       <x:c r="A407" s="61"/>
@@ -5891,7 +6350,8 @@
       <x:c r="H407" s="62"/>
       <x:c r="I407" s="62"/>
       <x:c r="J407" s="64"/>
-      <x:c r="K407" s="62"/>
+      <x:c r="K407" s="65"/>
+      <x:c r="L407" s="78"/>
     </x:row>
     <x:row r="408">
       <x:c r="A408" s="61"/>
@@ -5904,7 +6364,8 @@
       <x:c r="H408" s="62"/>
       <x:c r="I408" s="62"/>
       <x:c r="J408" s="64"/>
-      <x:c r="K408" s="62"/>
+      <x:c r="K408" s="65"/>
+      <x:c r="L408" s="78"/>
     </x:row>
     <x:row r="409">
       <x:c r="A409" s="61"/>
@@ -5917,7 +6378,8 @@
       <x:c r="H409" s="62"/>
       <x:c r="I409" s="62"/>
       <x:c r="J409" s="64"/>
-      <x:c r="K409" s="62"/>
+      <x:c r="K409" s="65"/>
+      <x:c r="L409" s="78"/>
     </x:row>
     <x:row r="410">
       <x:c r="A410" s="61"/>
@@ -5930,7 +6392,8 @@
       <x:c r="H410" s="62"/>
       <x:c r="I410" s="62"/>
       <x:c r="J410" s="64"/>
-      <x:c r="K410" s="62"/>
+      <x:c r="K410" s="65"/>
+      <x:c r="L410" s="78"/>
     </x:row>
     <x:row r="411">
       <x:c r="A411" s="61"/>
@@ -5943,7 +6406,8 @@
       <x:c r="H411" s="62"/>
       <x:c r="I411" s="62"/>
       <x:c r="J411" s="64"/>
-      <x:c r="K411" s="62"/>
+      <x:c r="K411" s="65"/>
+      <x:c r="L411" s="78"/>
     </x:row>
     <x:row r="412">
       <x:c r="A412" s="61"/>
@@ -5956,7 +6420,8 @@
       <x:c r="H412" s="62"/>
       <x:c r="I412" s="62"/>
       <x:c r="J412" s="64"/>
-      <x:c r="K412" s="62"/>
+      <x:c r="K412" s="65"/>
+      <x:c r="L412" s="78"/>
     </x:row>
     <x:row r="413">
       <x:c r="A413" s="61"/>
@@ -5969,7 +6434,8 @@
       <x:c r="H413" s="62"/>
       <x:c r="I413" s="62"/>
       <x:c r="J413" s="64"/>
-      <x:c r="K413" s="62"/>
+      <x:c r="K413" s="65"/>
+      <x:c r="L413" s="78"/>
     </x:row>
     <x:row r="414">
       <x:c r="A414" s="61"/>
@@ -5982,7 +6448,8 @@
       <x:c r="H414" s="62"/>
       <x:c r="I414" s="62"/>
       <x:c r="J414" s="64"/>
-      <x:c r="K414" s="62"/>
+      <x:c r="K414" s="65"/>
+      <x:c r="L414" s="78"/>
     </x:row>
     <x:row r="415">
       <x:c r="A415" s="61"/>
@@ -5995,7 +6462,8 @@
       <x:c r="H415" s="62"/>
       <x:c r="I415" s="62"/>
       <x:c r="J415" s="64"/>
-      <x:c r="K415" s="62"/>
+      <x:c r="K415" s="65"/>
+      <x:c r="L415" s="78"/>
     </x:row>
     <x:row r="416">
       <x:c r="A416" s="61"/>
@@ -6008,7 +6476,8 @@
       <x:c r="H416" s="62"/>
       <x:c r="I416" s="62"/>
       <x:c r="J416" s="64"/>
-      <x:c r="K416" s="62"/>
+      <x:c r="K416" s="65"/>
+      <x:c r="L416" s="78"/>
     </x:row>
     <x:row r="417">
       <x:c r="A417" s="61"/>
@@ -6021,7 +6490,8 @@
       <x:c r="H417" s="62"/>
       <x:c r="I417" s="62"/>
       <x:c r="J417" s="64"/>
-      <x:c r="K417" s="62"/>
+      <x:c r="K417" s="65"/>
+      <x:c r="L417" s="78"/>
     </x:row>
     <x:row r="418">
       <x:c r="A418" s="61"/>
@@ -6034,7 +6504,8 @@
       <x:c r="H418" s="62"/>
       <x:c r="I418" s="62"/>
       <x:c r="J418" s="64"/>
-      <x:c r="K418" s="62"/>
+      <x:c r="K418" s="65"/>
+      <x:c r="L418" s="78"/>
     </x:row>
     <x:row r="419">
       <x:c r="A419" s="61"/>
@@ -6047,7 +6518,8 @@
       <x:c r="H419" s="62"/>
       <x:c r="I419" s="62"/>
       <x:c r="J419" s="64"/>
-      <x:c r="K419" s="62"/>
+      <x:c r="K419" s="65"/>
+      <x:c r="L419" s="78"/>
     </x:row>
     <x:row r="420">
       <x:c r="A420" s="61"/>
@@ -6060,7 +6532,8 @@
       <x:c r="H420" s="62"/>
       <x:c r="I420" s="62"/>
       <x:c r="J420" s="64"/>
-      <x:c r="K420" s="62"/>
+      <x:c r="K420" s="65"/>
+      <x:c r="L420" s="78"/>
     </x:row>
     <x:row r="421">
       <x:c r="A421" s="61"/>
@@ -6073,7 +6546,8 @@
       <x:c r="H421" s="62"/>
       <x:c r="I421" s="62"/>
       <x:c r="J421" s="64"/>
-      <x:c r="K421" s="62"/>
+      <x:c r="K421" s="65"/>
+      <x:c r="L421" s="78"/>
     </x:row>
     <x:row r="422">
       <x:c r="A422" s="61"/>
@@ -6086,7 +6560,8 @@
       <x:c r="H422" s="62"/>
       <x:c r="I422" s="62"/>
       <x:c r="J422" s="64"/>
-      <x:c r="K422" s="62"/>
+      <x:c r="K422" s="65"/>
+      <x:c r="L422" s="78"/>
     </x:row>
     <x:row r="423">
       <x:c r="A423" s="61"/>
@@ -6099,7 +6574,8 @@
       <x:c r="H423" s="62"/>
       <x:c r="I423" s="62"/>
       <x:c r="J423" s="64"/>
-      <x:c r="K423" s="62"/>
+      <x:c r="K423" s="65"/>
+      <x:c r="L423" s="78"/>
     </x:row>
     <x:row r="424">
       <x:c r="A424" s="61"/>
@@ -6112,7 +6588,8 @@
       <x:c r="H424" s="62"/>
       <x:c r="I424" s="62"/>
       <x:c r="J424" s="64"/>
-      <x:c r="K424" s="62"/>
+      <x:c r="K424" s="65"/>
+      <x:c r="L424" s="78"/>
     </x:row>
     <x:row r="425">
       <x:c r="A425" s="61"/>
@@ -6125,7 +6602,8 @@
       <x:c r="H425" s="62"/>
       <x:c r="I425" s="62"/>
       <x:c r="J425" s="64"/>
-      <x:c r="K425" s="62"/>
+      <x:c r="K425" s="65"/>
+      <x:c r="L425" s="78"/>
     </x:row>
     <x:row r="426">
       <x:c r="A426" s="61"/>
@@ -6138,7 +6616,8 @@
       <x:c r="H426" s="62"/>
       <x:c r="I426" s="62"/>
       <x:c r="J426" s="64"/>
-      <x:c r="K426" s="62"/>
+      <x:c r="K426" s="65"/>
+      <x:c r="L426" s="78"/>
     </x:row>
     <x:row r="427">
       <x:c r="A427" s="61"/>
@@ -6151,7 +6630,8 @@
       <x:c r="H427" s="62"/>
       <x:c r="I427" s="62"/>
       <x:c r="J427" s="64"/>
-      <x:c r="K427" s="62"/>
+      <x:c r="K427" s="65"/>
+      <x:c r="L427" s="78"/>
     </x:row>
     <x:row r="428">
       <x:c r="A428" s="61"/>
@@ -6164,7 +6644,8 @@
       <x:c r="H428" s="62"/>
       <x:c r="I428" s="62"/>
       <x:c r="J428" s="64"/>
-      <x:c r="K428" s="62"/>
+      <x:c r="K428" s="65"/>
+      <x:c r="L428" s="78"/>
     </x:row>
     <x:row r="429">
       <x:c r="A429" s="61"/>
@@ -6177,7 +6658,8 @@
       <x:c r="H429" s="62"/>
       <x:c r="I429" s="62"/>
       <x:c r="J429" s="64"/>
-      <x:c r="K429" s="62"/>
+      <x:c r="K429" s="65"/>
+      <x:c r="L429" s="78"/>
     </x:row>
     <x:row r="430">
       <x:c r="A430" s="61"/>
@@ -6190,7 +6672,8 @@
       <x:c r="H430" s="62"/>
       <x:c r="I430" s="62"/>
       <x:c r="J430" s="64"/>
-      <x:c r="K430" s="62"/>
+      <x:c r="K430" s="65"/>
+      <x:c r="L430" s="78"/>
     </x:row>
     <x:row r="431">
       <x:c r="A431" s="61"/>
@@ -6203,7 +6686,8 @@
       <x:c r="H431" s="62"/>
       <x:c r="I431" s="62"/>
       <x:c r="J431" s="64"/>
-      <x:c r="K431" s="62"/>
+      <x:c r="K431" s="65"/>
+      <x:c r="L431" s="78"/>
     </x:row>
     <x:row r="432">
       <x:c r="A432" s="61"/>
@@ -6216,7 +6700,8 @@
       <x:c r="H432" s="62"/>
       <x:c r="I432" s="62"/>
       <x:c r="J432" s="64"/>
-      <x:c r="K432" s="62"/>
+      <x:c r="K432" s="65"/>
+      <x:c r="L432" s="78"/>
     </x:row>
     <x:row r="433">
       <x:c r="A433" s="61"/>
@@ -6229,7 +6714,8 @@
       <x:c r="H433" s="62"/>
       <x:c r="I433" s="62"/>
       <x:c r="J433" s="64"/>
-      <x:c r="K433" s="62"/>
+      <x:c r="K433" s="65"/>
+      <x:c r="L433" s="78"/>
     </x:row>
     <x:row r="434">
       <x:c r="A434" s="61"/>
@@ -6242,7 +6728,8 @@
       <x:c r="H434" s="62"/>
       <x:c r="I434" s="62"/>
       <x:c r="J434" s="64"/>
-      <x:c r="K434" s="62"/>
+      <x:c r="K434" s="65"/>
+      <x:c r="L434" s="78"/>
     </x:row>
     <x:row r="435">
       <x:c r="A435" s="61"/>
@@ -6255,7 +6742,8 @@
       <x:c r="H435" s="62"/>
       <x:c r="I435" s="62"/>
       <x:c r="J435" s="64"/>
-      <x:c r="K435" s="62"/>
+      <x:c r="K435" s="65"/>
+      <x:c r="L435" s="78"/>
     </x:row>
     <x:row r="436">
       <x:c r="A436" s="61"/>
@@ -6268,7 +6756,8 @@
       <x:c r="H436" s="62"/>
       <x:c r="I436" s="62"/>
       <x:c r="J436" s="64"/>
-      <x:c r="K436" s="62"/>
+      <x:c r="K436" s="65"/>
+      <x:c r="L436" s="78"/>
     </x:row>
     <x:row r="437">
       <x:c r="A437" s="61"/>
@@ -6281,7 +6770,8 @@
       <x:c r="H437" s="62"/>
       <x:c r="I437" s="62"/>
       <x:c r="J437" s="64"/>
-      <x:c r="K437" s="62"/>
+      <x:c r="K437" s="65"/>
+      <x:c r="L437" s="78"/>
     </x:row>
     <x:row r="438">
       <x:c r="A438" s="61"/>
@@ -6294,7 +6784,8 @@
       <x:c r="H438" s="62"/>
       <x:c r="I438" s="62"/>
       <x:c r="J438" s="64"/>
-      <x:c r="K438" s="62"/>
+      <x:c r="K438" s="65"/>
+      <x:c r="L438" s="78"/>
     </x:row>
     <x:row r="439">
       <x:c r="A439" s="61"/>
@@ -6307,7 +6798,8 @@
       <x:c r="H439" s="62"/>
       <x:c r="I439" s="62"/>
       <x:c r="J439" s="64"/>
-      <x:c r="K439" s="62"/>
+      <x:c r="K439" s="65"/>
+      <x:c r="L439" s="78"/>
     </x:row>
     <x:row r="440">
       <x:c r="A440" s="61"/>
@@ -6320,7 +6812,8 @@
       <x:c r="H440" s="62"/>
       <x:c r="I440" s="62"/>
       <x:c r="J440" s="64"/>
-      <x:c r="K440" s="62"/>
+      <x:c r="K440" s="65"/>
+      <x:c r="L440" s="78"/>
     </x:row>
     <x:row r="441">
       <x:c r="A441" s="61"/>
@@ -6333,7 +6826,8 @@
       <x:c r="H441" s="62"/>
       <x:c r="I441" s="62"/>
       <x:c r="J441" s="64"/>
-      <x:c r="K441" s="62"/>
+      <x:c r="K441" s="65"/>
+      <x:c r="L441" s="78"/>
     </x:row>
     <x:row r="442">
       <x:c r="A442" s="61"/>
@@ -6346,7 +6840,8 @@
       <x:c r="H442" s="62"/>
       <x:c r="I442" s="62"/>
       <x:c r="J442" s="64"/>
-      <x:c r="K442" s="62"/>
+      <x:c r="K442" s="65"/>
+      <x:c r="L442" s="78"/>
     </x:row>
     <x:row r="443">
       <x:c r="A443" s="61"/>
@@ -6359,7 +6854,8 @@
       <x:c r="H443" s="62"/>
       <x:c r="I443" s="62"/>
       <x:c r="J443" s="64"/>
-      <x:c r="K443" s="62"/>
+      <x:c r="K443" s="65"/>
+      <x:c r="L443" s="78"/>
     </x:row>
     <x:row r="444">
       <x:c r="A444" s="61"/>
@@ -6372,7 +6868,8 @@
       <x:c r="H444" s="62"/>
       <x:c r="I444" s="62"/>
       <x:c r="J444" s="64"/>
-      <x:c r="K444" s="62"/>
+      <x:c r="K444" s="65"/>
+      <x:c r="L444" s="78"/>
     </x:row>
     <x:row r="445">
       <x:c r="A445" s="61"/>
@@ -6385,7 +6882,8 @@
       <x:c r="H445" s="62"/>
       <x:c r="I445" s="62"/>
       <x:c r="J445" s="64"/>
-      <x:c r="K445" s="62"/>
+      <x:c r="K445" s="65"/>
+      <x:c r="L445" s="78"/>
     </x:row>
     <x:row r="446">
       <x:c r="A446" s="61"/>
@@ -6398,7 +6896,8 @@
       <x:c r="H446" s="62"/>
       <x:c r="I446" s="62"/>
       <x:c r="J446" s="64"/>
-      <x:c r="K446" s="62"/>
+      <x:c r="K446" s="65"/>
+      <x:c r="L446" s="78"/>
     </x:row>
     <x:row r="447">
       <x:c r="A447" s="61"/>
@@ -6411,7 +6910,8 @@
       <x:c r="H447" s="62"/>
       <x:c r="I447" s="62"/>
       <x:c r="J447" s="64"/>
-      <x:c r="K447" s="62"/>
+      <x:c r="K447" s="65"/>
+      <x:c r="L447" s="78"/>
     </x:row>
     <x:row r="448">
       <x:c r="A448" s="61"/>
@@ -6424,7 +6924,8 @@
       <x:c r="H448" s="62"/>
       <x:c r="I448" s="62"/>
       <x:c r="J448" s="64"/>
-      <x:c r="K448" s="62"/>
+      <x:c r="K448" s="65"/>
+      <x:c r="L448" s="78"/>
     </x:row>
     <x:row r="449">
       <x:c r="A449" s="61"/>
@@ -6437,7 +6938,8 @@
       <x:c r="H449" s="62"/>
       <x:c r="I449" s="62"/>
       <x:c r="J449" s="64"/>
-      <x:c r="K449" s="62"/>
+      <x:c r="K449" s="65"/>
+      <x:c r="L449" s="78"/>
     </x:row>
     <x:row r="450">
       <x:c r="A450" s="61"/>
@@ -6450,7 +6952,8 @@
       <x:c r="H450" s="62"/>
       <x:c r="I450" s="62"/>
       <x:c r="J450" s="64"/>
-      <x:c r="K450" s="62"/>
+      <x:c r="K450" s="65"/>
+      <x:c r="L450" s="78"/>
     </x:row>
     <x:row r="451">
       <x:c r="A451" s="61"/>
@@ -6463,7 +6966,8 @@
       <x:c r="H451" s="62"/>
       <x:c r="I451" s="62"/>
       <x:c r="J451" s="64"/>
-      <x:c r="K451" s="62"/>
+      <x:c r="K451" s="65"/>
+      <x:c r="L451" s="78"/>
     </x:row>
     <x:row r="452">
       <x:c r="A452" s="61"/>
@@ -6476,7 +6980,8 @@
       <x:c r="H452" s="62"/>
       <x:c r="I452" s="62"/>
       <x:c r="J452" s="64"/>
-      <x:c r="K452" s="62"/>
+      <x:c r="K452" s="65"/>
+      <x:c r="L452" s="78"/>
     </x:row>
     <x:row r="453">
       <x:c r="A453" s="61"/>
@@ -6489,7 +6994,8 @@
       <x:c r="H453" s="62"/>
       <x:c r="I453" s="62"/>
       <x:c r="J453" s="64"/>
-      <x:c r="K453" s="62"/>
+      <x:c r="K453" s="65"/>
+      <x:c r="L453" s="78"/>
     </x:row>
     <x:row r="454">
       <x:c r="A454" s="61"/>
@@ -6502,7 +7008,8 @@
       <x:c r="H454" s="62"/>
       <x:c r="I454" s="62"/>
       <x:c r="J454" s="64"/>
-      <x:c r="K454" s="62"/>
+      <x:c r="K454" s="65"/>
+      <x:c r="L454" s="78"/>
     </x:row>
     <x:row r="455">
       <x:c r="A455" s="61"/>
@@ -6515,7 +7022,8 @@
       <x:c r="H455" s="62"/>
       <x:c r="I455" s="62"/>
       <x:c r="J455" s="64"/>
-      <x:c r="K455" s="62"/>
+      <x:c r="K455" s="65"/>
+      <x:c r="L455" s="78"/>
     </x:row>
     <x:row r="456">
       <x:c r="A456" s="61"/>
@@ -6528,7 +7036,8 @@
       <x:c r="H456" s="62"/>
       <x:c r="I456" s="62"/>
       <x:c r="J456" s="64"/>
-      <x:c r="K456" s="62"/>
+      <x:c r="K456" s="65"/>
+      <x:c r="L456" s="78"/>
     </x:row>
     <x:row r="457">
       <x:c r="A457" s="61"/>
@@ -6541,7 +7050,8 @@
       <x:c r="H457" s="62"/>
       <x:c r="I457" s="62"/>
       <x:c r="J457" s="64"/>
-      <x:c r="K457" s="62"/>
+      <x:c r="K457" s="65"/>
+      <x:c r="L457" s="78"/>
     </x:row>
     <x:row r="458">
       <x:c r="A458" s="61"/>
@@ -6554,7 +7064,8 @@
       <x:c r="H458" s="62"/>
       <x:c r="I458" s="62"/>
       <x:c r="J458" s="64"/>
-      <x:c r="K458" s="62"/>
+      <x:c r="K458" s="65"/>
+      <x:c r="L458" s="78"/>
     </x:row>
     <x:row r="459">
       <x:c r="A459" s="61"/>
@@ -6567,7 +7078,8 @@
       <x:c r="H459" s="62"/>
       <x:c r="I459" s="62"/>
       <x:c r="J459" s="64"/>
-      <x:c r="K459" s="62"/>
+      <x:c r="K459" s="65"/>
+      <x:c r="L459" s="78"/>
     </x:row>
     <x:row r="460">
       <x:c r="A460" s="61"/>
@@ -6580,7 +7092,8 @@
       <x:c r="H460" s="62"/>
       <x:c r="I460" s="62"/>
       <x:c r="J460" s="64"/>
-      <x:c r="K460" s="62"/>
+      <x:c r="K460" s="65"/>
+      <x:c r="L460" s="78"/>
     </x:row>
     <x:row r="461">
       <x:c r="A461" s="61"/>
@@ -6593,7 +7106,8 @@
       <x:c r="H461" s="62"/>
       <x:c r="I461" s="62"/>
       <x:c r="J461" s="64"/>
-      <x:c r="K461" s="62"/>
+      <x:c r="K461" s="65"/>
+      <x:c r="L461" s="78"/>
     </x:row>
     <x:row r="462">
       <x:c r="A462" s="61"/>
@@ -6606,7 +7120,8 @@
       <x:c r="H462" s="62"/>
       <x:c r="I462" s="62"/>
       <x:c r="J462" s="64"/>
-      <x:c r="K462" s="62"/>
+      <x:c r="K462" s="65"/>
+      <x:c r="L462" s="78"/>
     </x:row>
     <x:row r="463">
       <x:c r="A463" s="61"/>
@@ -6619,7 +7134,8 @@
       <x:c r="H463" s="62"/>
       <x:c r="I463" s="62"/>
       <x:c r="J463" s="64"/>
-      <x:c r="K463" s="62"/>
+      <x:c r="K463" s="65"/>
+      <x:c r="L463" s="78"/>
     </x:row>
     <x:row r="464">
       <x:c r="A464" s="61"/>
@@ -6632,7 +7148,8 @@
       <x:c r="H464" s="62"/>
       <x:c r="I464" s="62"/>
       <x:c r="J464" s="64"/>
-      <x:c r="K464" s="62"/>
+      <x:c r="K464" s="65"/>
+      <x:c r="L464" s="78"/>
     </x:row>
     <x:row r="465">
       <x:c r="A465" s="61"/>
@@ -6645,7 +7162,8 @@
       <x:c r="H465" s="62"/>
       <x:c r="I465" s="62"/>
       <x:c r="J465" s="64"/>
-      <x:c r="K465" s="62"/>
+      <x:c r="K465" s="65"/>
+      <x:c r="L465" s="78"/>
     </x:row>
     <x:row r="466">
       <x:c r="A466" s="61"/>
@@ -6658,7 +7176,8 @@
       <x:c r="H466" s="62"/>
       <x:c r="I466" s="62"/>
       <x:c r="J466" s="64"/>
-      <x:c r="K466" s="62"/>
+      <x:c r="K466" s="65"/>
+      <x:c r="L466" s="78"/>
     </x:row>
     <x:row r="467">
       <x:c r="A467" s="61"/>
@@ -6671,7 +7190,8 @@
       <x:c r="H467" s="62"/>
       <x:c r="I467" s="62"/>
       <x:c r="J467" s="64"/>
-      <x:c r="K467" s="62"/>
+      <x:c r="K467" s="65"/>
+      <x:c r="L467" s="78"/>
     </x:row>
     <x:row r="468">
       <x:c r="A468" s="61"/>
@@ -6684,7 +7204,8 @@
       <x:c r="H468" s="62"/>
       <x:c r="I468" s="62"/>
       <x:c r="J468" s="64"/>
-      <x:c r="K468" s="62"/>
+      <x:c r="K468" s="65"/>
+      <x:c r="L468" s="78"/>
     </x:row>
     <x:row r="469">
       <x:c r="A469" s="61"/>
@@ -6697,7 +7218,8 @@
       <x:c r="H469" s="62"/>
       <x:c r="I469" s="62"/>
       <x:c r="J469" s="64"/>
-      <x:c r="K469" s="62"/>
+      <x:c r="K469" s="65"/>
+      <x:c r="L469" s="78"/>
     </x:row>
     <x:row r="470">
       <x:c r="A470" s="61"/>
@@ -6710,7 +7232,8 @@
       <x:c r="H470" s="62"/>
       <x:c r="I470" s="62"/>
       <x:c r="J470" s="64"/>
-      <x:c r="K470" s="62"/>
+      <x:c r="K470" s="65"/>
+      <x:c r="L470" s="78"/>
     </x:row>
     <x:row r="471">
       <x:c r="A471" s="61"/>
@@ -6723,7 +7246,8 @@
       <x:c r="H471" s="62"/>
       <x:c r="I471" s="62"/>
       <x:c r="J471" s="64"/>
-      <x:c r="K471" s="62"/>
+      <x:c r="K471" s="65"/>
+      <x:c r="L471" s="78"/>
     </x:row>
     <x:row r="472">
       <x:c r="A472" s="61"/>
@@ -6736,7 +7260,8 @@
       <x:c r="H472" s="62"/>
       <x:c r="I472" s="62"/>
       <x:c r="J472" s="64"/>
-      <x:c r="K472" s="62"/>
+      <x:c r="K472" s="65"/>
+      <x:c r="L472" s="78"/>
     </x:row>
     <x:row r="473">
       <x:c r="A473" s="61"/>
@@ -6749,7 +7274,8 @@
       <x:c r="H473" s="62"/>
       <x:c r="I473" s="62"/>
       <x:c r="J473" s="64"/>
-      <x:c r="K473" s="62"/>
+      <x:c r="K473" s="65"/>
+      <x:c r="L473" s="78"/>
     </x:row>
     <x:row r="474">
       <x:c r="A474" s="61"/>
@@ -6762,7 +7288,8 @@
       <x:c r="H474" s="62"/>
       <x:c r="I474" s="62"/>
       <x:c r="J474" s="64"/>
-      <x:c r="K474" s="62"/>
+      <x:c r="K474" s="65"/>
+      <x:c r="L474" s="78"/>
     </x:row>
     <x:row r="475">
       <x:c r="A475" s="61"/>
@@ -6775,7 +7302,8 @@
       <x:c r="H475" s="62"/>
       <x:c r="I475" s="62"/>
       <x:c r="J475" s="64"/>
-      <x:c r="K475" s="62"/>
+      <x:c r="K475" s="65"/>
+      <x:c r="L475" s="78"/>
     </x:row>
     <x:row r="476">
       <x:c r="A476" s="61"/>
@@ -6788,7 +7316,8 @@
       <x:c r="H476" s="62"/>
       <x:c r="I476" s="62"/>
       <x:c r="J476" s="64"/>
-      <x:c r="K476" s="62"/>
+      <x:c r="K476" s="65"/>
+      <x:c r="L476" s="78"/>
     </x:row>
     <x:row r="477">
       <x:c r="A477" s="61"/>
@@ -6801,7 +7330,8 @@
       <x:c r="H477" s="62"/>
       <x:c r="I477" s="62"/>
       <x:c r="J477" s="64"/>
-      <x:c r="K477" s="62"/>
+      <x:c r="K477" s="65"/>
+      <x:c r="L477" s="78"/>
     </x:row>
     <x:row r="478">
       <x:c r="A478" s="61"/>
@@ -6814,7 +7344,8 @@
       <x:c r="H478" s="62"/>
       <x:c r="I478" s="62"/>
       <x:c r="J478" s="64"/>
-      <x:c r="K478" s="62"/>
+      <x:c r="K478" s="65"/>
+      <x:c r="L478" s="78"/>
     </x:row>
     <x:row r="479">
       <x:c r="A479" s="61"/>
@@ -6827,7 +7358,8 @@
       <x:c r="H479" s="62"/>
       <x:c r="I479" s="62"/>
       <x:c r="J479" s="64"/>
-      <x:c r="K479" s="62"/>
+      <x:c r="K479" s="65"/>
+      <x:c r="L479" s="78"/>
     </x:row>
     <x:row r="480">
       <x:c r="A480" s="61"/>
@@ -6840,7 +7372,8 @@
       <x:c r="H480" s="62"/>
       <x:c r="I480" s="62"/>
       <x:c r="J480" s="64"/>
-      <x:c r="K480" s="62"/>
+      <x:c r="K480" s="65"/>
+      <x:c r="L480" s="78"/>
     </x:row>
     <x:row r="481">
       <x:c r="A481" s="61"/>
@@ -6853,7 +7386,8 @@
       <x:c r="H481" s="62"/>
       <x:c r="I481" s="62"/>
       <x:c r="J481" s="64"/>
-      <x:c r="K481" s="62"/>
+      <x:c r="K481" s="65"/>
+      <x:c r="L481" s="78"/>
     </x:row>
     <x:row r="482">
       <x:c r="A482" s="61"/>
@@ -6866,7 +7400,8 @@
       <x:c r="H482" s="62"/>
       <x:c r="I482" s="62"/>
       <x:c r="J482" s="64"/>
-      <x:c r="K482" s="62"/>
+      <x:c r="K482" s="65"/>
+      <x:c r="L482" s="78"/>
     </x:row>
     <x:row r="483">
       <x:c r="A483" s="61"/>
@@ -6879,7 +7414,8 @@
       <x:c r="H483" s="62"/>
       <x:c r="I483" s="62"/>
       <x:c r="J483" s="64"/>
-      <x:c r="K483" s="62"/>
+      <x:c r="K483" s="65"/>
+      <x:c r="L483" s="78"/>
     </x:row>
     <x:row r="484">
       <x:c r="A484" s="61"/>
@@ -6892,7 +7428,8 @@
       <x:c r="H484" s="62"/>
       <x:c r="I484" s="62"/>
       <x:c r="J484" s="64"/>
-      <x:c r="K484" s="62"/>
+      <x:c r="K484" s="65"/>
+      <x:c r="L484" s="78"/>
     </x:row>
     <x:row r="485">
       <x:c r="A485" s="61"/>
@@ -6905,7 +7442,8 @@
       <x:c r="H485" s="62"/>
       <x:c r="I485" s="62"/>
       <x:c r="J485" s="64"/>
-      <x:c r="K485" s="62"/>
+      <x:c r="K485" s="65"/>
+      <x:c r="L485" s="78"/>
     </x:row>
     <x:row r="486">
       <x:c r="A486" s="61"/>
@@ -6918,7 +7456,8 @@
       <x:c r="H486" s="62"/>
       <x:c r="I486" s="62"/>
       <x:c r="J486" s="64"/>
-      <x:c r="K486" s="62"/>
+      <x:c r="K486" s="65"/>
+      <x:c r="L486" s="78"/>
     </x:row>
     <x:row r="487">
       <x:c r="A487" s="61"/>
@@ -6931,7 +7470,8 @@
       <x:c r="H487" s="62"/>
       <x:c r="I487" s="62"/>
       <x:c r="J487" s="64"/>
-      <x:c r="K487" s="62"/>
+      <x:c r="K487" s="65"/>
+      <x:c r="L487" s="78"/>
     </x:row>
     <x:row r="488">
       <x:c r="A488" s="61"/>
@@ -6944,7 +7484,8 @@
       <x:c r="H488" s="62"/>
       <x:c r="I488" s="62"/>
       <x:c r="J488" s="64"/>
-      <x:c r="K488" s="62"/>
+      <x:c r="K488" s="65"/>
+      <x:c r="L488" s="78"/>
     </x:row>
     <x:row r="489">
       <x:c r="A489" s="61"/>
@@ -6957,7 +7498,8 @@
       <x:c r="H489" s="62"/>
       <x:c r="I489" s="62"/>
       <x:c r="J489" s="64"/>
-      <x:c r="K489" s="62"/>
+      <x:c r="K489" s="65"/>
+      <x:c r="L489" s="78"/>
     </x:row>
     <x:row r="490">
       <x:c r="A490" s="61"/>
@@ -6970,7 +7512,8 @@
       <x:c r="H490" s="62"/>
       <x:c r="I490" s="62"/>
       <x:c r="J490" s="64"/>
-      <x:c r="K490" s="62"/>
+      <x:c r="K490" s="65"/>
+      <x:c r="L490" s="78"/>
     </x:row>
     <x:row r="491">
       <x:c r="A491" s="61"/>
@@ -6983,7 +7526,8 @@
       <x:c r="H491" s="62"/>
       <x:c r="I491" s="62"/>
       <x:c r="J491" s="64"/>
-      <x:c r="K491" s="62"/>
+      <x:c r="K491" s="65"/>
+      <x:c r="L491" s="78"/>
     </x:row>
     <x:row r="492">
       <x:c r="A492" s="61"/>
@@ -6996,7 +7540,8 @@
       <x:c r="H492" s="62"/>
       <x:c r="I492" s="62"/>
       <x:c r="J492" s="64"/>
-      <x:c r="K492" s="62"/>
+      <x:c r="K492" s="65"/>
+      <x:c r="L492" s="78"/>
     </x:row>
     <x:row r="493">
       <x:c r="A493" s="61"/>
@@ -7009,7 +7554,8 @@
       <x:c r="H493" s="62"/>
       <x:c r="I493" s="62"/>
       <x:c r="J493" s="64"/>
-      <x:c r="K493" s="62"/>
+      <x:c r="K493" s="65"/>
+      <x:c r="L493" s="78"/>
     </x:row>
     <x:row r="494">
       <x:c r="A494" s="61"/>
@@ -7022,7 +7568,8 @@
       <x:c r="H494" s="62"/>
       <x:c r="I494" s="62"/>
       <x:c r="J494" s="64"/>
-      <x:c r="K494" s="62"/>
+      <x:c r="K494" s="65"/>
+      <x:c r="L494" s="78"/>
     </x:row>
     <x:row r="495">
       <x:c r="A495" s="61"/>
@@ -7035,7 +7582,8 @@
       <x:c r="H495" s="62"/>
       <x:c r="I495" s="62"/>
       <x:c r="J495" s="64"/>
-      <x:c r="K495" s="62"/>
+      <x:c r="K495" s="65"/>
+      <x:c r="L495" s="78"/>
     </x:row>
     <x:row r="496">
       <x:c r="A496" s="61"/>
@@ -7048,7 +7596,8 @@
       <x:c r="H496" s="62"/>
       <x:c r="I496" s="62"/>
       <x:c r="J496" s="64"/>
-      <x:c r="K496" s="62"/>
+      <x:c r="K496" s="65"/>
+      <x:c r="L496" s="78"/>
     </x:row>
     <x:row r="497">
       <x:c r="A497" s="61"/>
@@ -7061,7 +7610,8 @@
       <x:c r="H497" s="62"/>
       <x:c r="I497" s="62"/>
       <x:c r="J497" s="64"/>
-      <x:c r="K497" s="62"/>
+      <x:c r="K497" s="65"/>
+      <x:c r="L497" s="78"/>
     </x:row>
     <x:row r="498">
       <x:c r="A498" s="61"/>
@@ -7074,7 +7624,8 @@
       <x:c r="H498" s="62"/>
       <x:c r="I498" s="62"/>
       <x:c r="J498" s="64"/>
-      <x:c r="K498" s="62"/>
+      <x:c r="K498" s="65"/>
+      <x:c r="L498" s="78"/>
     </x:row>
     <x:row r="499">
       <x:c r="A499" s="61"/>
@@ -7087,7 +7638,8 @@
       <x:c r="H499" s="62"/>
       <x:c r="I499" s="62"/>
       <x:c r="J499" s="64"/>
-      <x:c r="K499" s="62"/>
+      <x:c r="K499" s="65"/>
+      <x:c r="L499" s="78"/>
     </x:row>
     <x:row r="500">
       <x:c r="A500" s="61"/>
@@ -7100,14 +7652,15 @@
       <x:c r="H500" s="62"/>
       <x:c r="I500" s="62"/>
       <x:c r="J500" s="64"/>
-      <x:c r="K500" s="62"/>
+      <x:c r="K500" s="66"/>
+      <x:c r="L500" s="78"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A2:J2"/>
-    <x:mergeCell ref="A3:J3"/>
+    <x:mergeCell ref="A2:L2"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
-  <x:dataValidations count="4">
+  <x:dataValidations count="5">
     <x:dataValidation type="list" sqref="B6:B500">
       <x:formula1>"A,B,C,D,E,F,TMU"</x:formula1>
     </x:dataValidation>
@@ -7121,10 +7674,14 @@
     <x:dataValidation type="list" sqref="K6:K500">
       <x:formula1>"Yes,No"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="L6:L500">
+      <x:formula1>0</x:formula1>
+      <x:formula2>99999</x:formula2>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8203558c6424328"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08328b766904430a"/>
   </x:tableParts>
 </x:worksheet>
 </file>